--- a/Datos limpios/Pricing diario/2015/Cebada.xlsx
+++ b/Datos limpios/Pricing diario/2015/Cebada.xlsx
@@ -1,24 +1,71 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5528ac80b6f1b5d4/Documents/Maestria en Ciencia de Datos/1. Primer semestre/Análisis inteligente de datos/trabajo-final-belenmaldonado1/Datos limpios/Pricing diario/2015/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="17" documentId="11_AB635DDC8F79A8536E3CA493EA7BD2724ACE2D1E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB3D9E24-699B-4992-982B-604C44E75477}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="12">
+  <si>
+    <t>FECHA_OPERACION</t>
+  </si>
+  <si>
+    <t>CONTRATO</t>
+  </si>
+  <si>
+    <t>CONTRATO_RECTIFICACION</t>
+  </si>
+  <si>
+    <t>CONTRATO_ANULACION</t>
+  </si>
+  <si>
+    <t>CONTRATO_PRECIO_HECHO</t>
+  </si>
+  <si>
+    <t>FIJACION</t>
+  </si>
+  <si>
+    <t>FIJACION_RECTIFICACION</t>
+  </si>
+  <si>
+    <t>FIJACION_ANULACION</t>
+  </si>
+  <si>
+    <t>FIJACIONES</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>PRODUCTO</t>
+  </si>
+  <si>
+    <t>CEBADA</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -67,13 +114,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -81,37 +136,37 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -145,6 +200,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -179,9 +235,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -354,71 +411,49 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K244"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>FECHA_OPERACION</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>CONTRATO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>CONTRATO_RECTIFICACION</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>CONTRATO_ANULACION</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>CONTRATO_PRECIO_HECHO</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>FIJACION</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>FIJACION_RECTIFICACION</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>FIJACION_ANULACION</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>FIJACIONES</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>PRODUCTO</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>42006</v>
       </c>
@@ -449,13 +484,11 @@
       <c r="J2">
         <v>630</v>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
+      <c r="K2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>42009</v>
       </c>
@@ -486,13 +519,11 @@
       <c r="J3">
         <v>2246</v>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
+      <c r="K3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>42010</v>
       </c>
@@ -523,13 +554,11 @@
       <c r="J4">
         <v>4096.58</v>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
+      <c r="K4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>42011</v>
       </c>
@@ -560,13 +589,11 @@
       <c r="J5">
         <v>1230</v>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
+      <c r="K5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>42012</v>
       </c>
@@ -597,13 +624,11 @@
       <c r="J6">
         <v>3510</v>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
+      <c r="K6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>42013</v>
       </c>
@@ -634,13 +659,11 @@
       <c r="J7">
         <v>4498</v>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
+      <c r="K7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>42016</v>
       </c>
@@ -671,13 +694,11 @@
       <c r="J8">
         <v>3364</v>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
+      <c r="K8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>42017</v>
       </c>
@@ -708,13 +729,11 @@
       <c r="J9">
         <v>31608</v>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
+      <c r="K9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>42018</v>
       </c>
@@ -745,13 +764,11 @@
       <c r="J10">
         <v>4915.46</v>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
+      <c r="K10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>42019</v>
       </c>
@@ -782,13 +799,11 @@
       <c r="J11">
         <v>6430</v>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
+      <c r="K11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>42020</v>
       </c>
@@ -819,13 +834,11 @@
       <c r="J12">
         <v>7305</v>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
+      <c r="K12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>42023</v>
       </c>
@@ -856,13 +869,11 @@
       <c r="J13">
         <v>2900</v>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
+      <c r="K13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>42024</v>
       </c>
@@ -893,13 +904,11 @@
       <c r="J14">
         <v>4100</v>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
+      <c r="K14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>42025</v>
       </c>
@@ -930,13 +939,11 @@
       <c r="J15">
         <v>1653</v>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
+      <c r="K15" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>42026</v>
       </c>
@@ -967,18 +974,16 @@
       <c r="J16">
         <v>5335</v>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
+      <c r="K16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>42027</v>
       </c>
       <c r="B17">
-        <v>8621.219999999999</v>
+        <v>8621.2199999999993</v>
       </c>
       <c r="C17">
         <v>1080</v>
@@ -987,7 +992,7 @@
         <v>0</v>
       </c>
       <c r="E17">
-        <v>9701.219999999999</v>
+        <v>9701.2199999999993</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1002,15 +1007,13 @@
         <v>0</v>
       </c>
       <c r="J17">
-        <v>9701.219999999999</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
+        <v>9701.2199999999993</v>
+      </c>
+      <c r="K17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>42030</v>
       </c>
@@ -1041,13 +1044,11 @@
       <c r="J18">
         <v>16269.6</v>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
+      <c r="K18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>42031</v>
       </c>
@@ -1078,13 +1079,11 @@
       <c r="J19">
         <v>13246.24</v>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
+      <c r="K19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>42032</v>
       </c>
@@ -1115,13 +1114,11 @@
       <c r="J20">
         <v>13594.38</v>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
+      <c r="K20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>42033</v>
       </c>
@@ -1152,13 +1149,11 @@
       <c r="J21">
         <v>28558.02</v>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
+      <c r="K21" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>42034</v>
       </c>
@@ -1189,13 +1184,11 @@
       <c r="J22">
         <v>41168</v>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
+      <c r="K22" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>42035</v>
       </c>
@@ -1224,15 +1217,13 @@
         <v>44.6</v>
       </c>
       <c r="J23">
-        <v>1034.6</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
+        <v>1034.5999999999999</v>
+      </c>
+      <c r="K23" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>42036</v>
       </c>
@@ -1263,13 +1254,11 @@
       <c r="J24">
         <v>199.17</v>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
+      <c r="K24" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>42037</v>
       </c>
@@ -1300,18 +1289,16 @@
       <c r="J25">
         <v>11200.85</v>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
+      <c r="K25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>42038</v>
       </c>
       <c r="B26">
-        <v>8198.030000000001</v>
+        <v>8198.0300000000007</v>
       </c>
       <c r="C26">
         <v>60</v>
@@ -1320,7 +1307,7 @@
         <v>1610</v>
       </c>
       <c r="E26">
-        <v>6648.030000000001</v>
+        <v>6648.0300000000007</v>
       </c>
       <c r="F26">
         <v>60</v>
@@ -1335,15 +1322,13 @@
         <v>60</v>
       </c>
       <c r="J26">
-        <v>6708.030000000001</v>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
+        <v>6708.0300000000007</v>
+      </c>
+      <c r="K26" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>42039</v>
       </c>
@@ -1374,13 +1359,11 @@
       <c r="J27">
         <v>11764.9</v>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
+      <c r="K27" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>42040</v>
       </c>
@@ -1411,13 +1394,11 @@
       <c r="J28">
         <v>3779.05</v>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
+      <c r="K28" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>42041</v>
       </c>
@@ -1448,13 +1429,11 @@
       <c r="J29">
         <v>7983.95</v>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
+      <c r="K29" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>42042</v>
       </c>
@@ -1485,13 +1464,11 @@
       <c r="J30">
         <v>28</v>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
+      <c r="K30" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>42044</v>
       </c>
@@ -1522,13 +1499,11 @@
       <c r="J31">
         <v>3646.63</v>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
+      <c r="K31" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>42045</v>
       </c>
@@ -1559,13 +1534,11 @@
       <c r="J32">
         <v>7588.35</v>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
+      <c r="K32" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>42046</v>
       </c>
@@ -1579,7 +1552,7 @@
         <v>0</v>
       </c>
       <c r="E33">
-        <v>4127.98</v>
+        <v>4127.9799999999996</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -1594,15 +1567,13 @@
         <v>0</v>
       </c>
       <c r="J33">
-        <v>4127.98</v>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
+        <v>4127.9799999999996</v>
+      </c>
+      <c r="K33" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>42047</v>
       </c>
@@ -1633,13 +1604,11 @@
       <c r="J34">
         <v>12347.34</v>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
+      <c r="K34" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>42048</v>
       </c>
@@ -1653,7 +1622,7 @@
         <v>1777.94</v>
       </c>
       <c r="E35">
-        <v>18305.65</v>
+        <v>18305.650000000001</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -1668,20 +1637,18 @@
         <v>0</v>
       </c>
       <c r="J35">
-        <v>18305.65</v>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
+        <v>18305.650000000001</v>
+      </c>
+      <c r="K35" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>42049</v>
       </c>
       <c r="B36">
-        <v>946.5799999999999</v>
+        <v>946.57999999999993</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -1690,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="E36">
-        <v>946.5799999999999</v>
+        <v>946.57999999999993</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -1705,15 +1672,13 @@
         <v>0</v>
       </c>
       <c r="J36">
-        <v>946.5799999999999</v>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
+        <v>946.57999999999993</v>
+      </c>
+      <c r="K36" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>42052</v>
       </c>
@@ -1744,13 +1709,11 @@
       <c r="J37">
         <v>6618.07</v>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
+      <c r="K37" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>42053</v>
       </c>
@@ -1781,24 +1744,22 @@
       <c r="J38">
         <v>3108</v>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
+      <c r="K38" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>42054</v>
       </c>
       <c r="B39">
-        <v>10394.22</v>
+        <v>10394.219999999999</v>
       </c>
       <c r="C39">
         <v>862.24</v>
       </c>
       <c r="D39">
-        <v>839.3099999999999</v>
+        <v>839.31</v>
       </c>
       <c r="E39">
         <v>10417.15</v>
@@ -1818,13 +1779,11 @@
       <c r="J39">
         <v>10717.15</v>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
+      <c r="K39" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>42055</v>
       </c>
@@ -1855,13 +1814,11 @@
       <c r="J40">
         <v>8191.25</v>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
+      <c r="K40" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>42056</v>
       </c>
@@ -1869,13 +1826,13 @@
         <v>30</v>
       </c>
       <c r="C41">
-        <v>285.54</v>
+        <v>285.54000000000002</v>
       </c>
       <c r="D41">
         <v>0</v>
       </c>
       <c r="E41">
-        <v>315.54</v>
+        <v>315.54000000000002</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -1890,15 +1847,13 @@
         <v>0</v>
       </c>
       <c r="J41">
-        <v>315.54</v>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
+        <v>315.54000000000002</v>
+      </c>
+      <c r="K41" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>42058</v>
       </c>
@@ -1929,13 +1884,11 @@
       <c r="J42">
         <v>4857.66</v>
       </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
+      <c r="K42" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>42059</v>
       </c>
@@ -1966,13 +1919,11 @@
       <c r="J43">
         <v>6458.25</v>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
+      <c r="K43" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>42060</v>
       </c>
@@ -2003,13 +1954,11 @@
       <c r="J44">
         <v>2356.52</v>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
+      <c r="K44" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <v>42061</v>
       </c>
@@ -2040,13 +1989,11 @@
       <c r="J45">
         <v>6505.81</v>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
+      <c r="K45" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <v>42062</v>
       </c>
@@ -2077,13 +2024,11 @@
       <c r="J46">
         <v>2640.04</v>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
+      <c r="K46" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
         <v>42065</v>
       </c>
@@ -2114,13 +2059,11 @@
       <c r="J47">
         <v>2590</v>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
+      <c r="K47" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
         <v>42066</v>
       </c>
@@ -2151,13 +2094,11 @@
       <c r="J48">
         <v>1183.42</v>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
+      <c r="K48" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
         <v>42067</v>
       </c>
@@ -2168,7 +2109,7 @@
         <v>124.44</v>
       </c>
       <c r="D49">
-        <v>55.23999999999999</v>
+        <v>55.239999999999988</v>
       </c>
       <c r="E49">
         <v>3346.11</v>
@@ -2188,13 +2129,11 @@
       <c r="J49">
         <v>3346.11</v>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
+      <c r="K49" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
         <v>42068</v>
       </c>
@@ -2225,13 +2164,11 @@
       <c r="J50">
         <v>1497.27</v>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
+      <c r="K50" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
         <v>42069</v>
       </c>
@@ -2262,13 +2199,11 @@
       <c r="J51">
         <v>3728.36</v>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
+      <c r="K51" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
         <v>42072</v>
       </c>
@@ -2299,13 +2234,11 @@
       <c r="J52">
         <v>3754.68</v>
       </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
+      <c r="K52" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
         <v>42073</v>
       </c>
@@ -2336,13 +2269,11 @@
       <c r="J53">
         <v>4418</v>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
+      <c r="K53" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
         <v>42074</v>
       </c>
@@ -2373,13 +2304,11 @@
       <c r="J54">
         <v>965</v>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
+      <c r="K54" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
         <v>42075</v>
       </c>
@@ -2410,13 +2339,11 @@
       <c r="J55">
         <v>1636</v>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
+      <c r="K55" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
         <v>42076</v>
       </c>
@@ -2447,13 +2374,11 @@
       <c r="J56">
         <v>610</v>
       </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
+      <c r="K56" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
         <v>42079</v>
       </c>
@@ -2484,13 +2409,11 @@
       <c r="J57">
         <v>3125.02</v>
       </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
+      <c r="K57" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
         <v>42080</v>
       </c>
@@ -2521,13 +2444,11 @@
       <c r="J58">
         <v>3067.06</v>
       </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
+      <c r="K58" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
         <v>42081</v>
       </c>
@@ -2558,18 +2479,16 @@
       <c r="J59">
         <v>1137.01</v>
       </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
+      <c r="K59" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
         <v>42082</v>
       </c>
       <c r="B60">
-        <v>8900.440000000001</v>
+        <v>8900.44</v>
       </c>
       <c r="C60">
         <v>605.62</v>
@@ -2578,7 +2497,7 @@
         <v>0</v>
       </c>
       <c r="E60">
-        <v>9506.060000000001</v>
+        <v>9506.0600000000013</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -2593,15 +2512,13 @@
         <v>0</v>
       </c>
       <c r="J60">
-        <v>9506.060000000001</v>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
+        <v>9506.0600000000013</v>
+      </c>
+      <c r="K60" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
         <v>42083</v>
       </c>
@@ -2632,13 +2549,11 @@
       <c r="J61">
         <v>1476.83</v>
       </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
+      <c r="K61" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
         <v>42084</v>
       </c>
@@ -2669,13 +2584,11 @@
       <c r="J62">
         <v>767.24</v>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
+      <c r="K62" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
         <v>42088</v>
       </c>
@@ -2706,13 +2619,11 @@
       <c r="J63">
         <v>1431.55</v>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
+      <c r="K63" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
         <v>42089</v>
       </c>
@@ -2743,13 +2654,11 @@
       <c r="J64">
         <v>2041.62</v>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
+      <c r="K64" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
         <v>42090</v>
       </c>
@@ -2780,13 +2689,11 @@
       <c r="J65">
         <v>687</v>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
+      <c r="K65" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
         <v>42091</v>
       </c>
@@ -2817,13 +2724,11 @@
       <c r="J66">
         <v>62.17</v>
       </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
+      <c r="K66" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
         <v>42093</v>
       </c>
@@ -2854,13 +2759,11 @@
       <c r="J67">
         <v>1268</v>
       </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
+      <c r="K67" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
         <v>42094</v>
       </c>
@@ -2891,13 +2794,11 @@
       <c r="J68">
         <v>560</v>
       </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
+      <c r="K68" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
         <v>42095</v>
       </c>
@@ -2928,13 +2829,11 @@
       <c r="J69">
         <v>1064</v>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
+      <c r="K69" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
         <v>42100</v>
       </c>
@@ -2965,13 +2864,11 @@
       <c r="J70">
         <v>436</v>
       </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
+      <c r="K70" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
         <v>42101</v>
       </c>
@@ -3002,13 +2899,11 @@
       <c r="J71">
         <v>2522.29</v>
       </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
+      <c r="K71" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
         <v>42102</v>
       </c>
@@ -3039,13 +2934,11 @@
       <c r="J72">
         <v>710</v>
       </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
+      <c r="K72" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
         <v>42103</v>
       </c>
@@ -3076,13 +2969,11 @@
       <c r="J73">
         <v>1095</v>
       </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
+      <c r="K73" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
         <v>42104</v>
       </c>
@@ -3113,13 +3004,11 @@
       <c r="J74">
         <v>328</v>
       </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
+      <c r="K74" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
         <v>42107</v>
       </c>
@@ -3150,13 +3039,11 @@
       <c r="J75">
         <v>120</v>
       </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
+      <c r="K75" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
         <v>42108</v>
       </c>
@@ -3187,13 +3074,11 @@
       <c r="J76">
         <v>2187</v>
       </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
+      <c r="K76" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
         <v>42109</v>
       </c>
@@ -3224,13 +3109,11 @@
       <c r="J77">
         <v>892.9</v>
       </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
+      <c r="K77" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
         <v>42110</v>
       </c>
@@ -3244,7 +3127,7 @@
         <v>0</v>
       </c>
       <c r="E78">
-        <v>536.0599999999999</v>
+        <v>536.05999999999995</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -3259,15 +3142,13 @@
         <v>0</v>
       </c>
       <c r="J78">
-        <v>536.0599999999999</v>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
+        <v>536.05999999999995</v>
+      </c>
+      <c r="K78" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
         <v>42111</v>
       </c>
@@ -3298,13 +3179,11 @@
       <c r="J79">
         <v>442</v>
       </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
+      <c r="K79" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
         <v>42114</v>
       </c>
@@ -3335,13 +3214,11 @@
       <c r="J80">
         <v>322.94</v>
       </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
+      <c r="K80" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
         <v>42115</v>
       </c>
@@ -3372,13 +3249,11 @@
       <c r="J81">
         <v>1603</v>
       </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
+      <c r="K81" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
         <v>42116</v>
       </c>
@@ -3409,13 +3284,11 @@
       <c r="J82">
         <v>728</v>
       </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
+      <c r="K82" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83" s="2">
         <v>42117</v>
       </c>
@@ -3446,13 +3319,11 @@
       <c r="J83">
         <v>2008.88</v>
       </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
+      <c r="K83" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
         <v>42118</v>
       </c>
@@ -3483,13 +3354,11 @@
       <c r="J84">
         <v>1230</v>
       </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
+      <c r="K84" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
         <v>42121</v>
       </c>
@@ -3520,13 +3389,11 @@
       <c r="J85">
         <v>860</v>
       </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
+      <c r="K85" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86" s="2">
         <v>42122</v>
       </c>
@@ -3557,13 +3424,11 @@
       <c r="J86">
         <v>15935</v>
       </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
+      <c r="K86" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A87" s="2">
         <v>42123</v>
       </c>
@@ -3594,13 +3459,11 @@
       <c r="J87">
         <v>1865</v>
       </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
+      <c r="K87" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A88" s="2">
         <v>42124</v>
       </c>
@@ -3631,18 +3494,16 @@
       <c r="J88">
         <v>121.22</v>
       </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
+      <c r="K88" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A89" s="2">
         <v>42128</v>
       </c>
       <c r="B89">
-        <v>1304.16</v>
+        <v>1304.1600000000001</v>
       </c>
       <c r="C89">
         <v>60</v>
@@ -3668,13 +3529,11 @@
       <c r="J89">
         <v>1364.16</v>
       </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
+      <c r="K89" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A90" s="2">
         <v>42129</v>
       </c>
@@ -3705,13 +3564,11 @@
       <c r="J90">
         <v>9.66</v>
       </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
+      <c r="K90" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91" s="2">
         <v>42130</v>
       </c>
@@ -3742,13 +3599,11 @@
       <c r="J91">
         <v>420</v>
       </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
+      <c r="K91" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A92" s="2">
         <v>42131</v>
       </c>
@@ -3779,13 +3634,11 @@
       <c r="J92">
         <v>30</v>
       </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
+      <c r="K92" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A93" s="2">
         <v>42132</v>
       </c>
@@ -3816,13 +3669,11 @@
       <c r="J93">
         <v>10521.84</v>
       </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
+      <c r="K93" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A94" s="2">
         <v>42135</v>
       </c>
@@ -3853,13 +3704,11 @@
       <c r="J94">
         <v>240.78</v>
       </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
+      <c r="K94" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A95" s="2">
         <v>42136</v>
       </c>
@@ -3890,13 +3739,11 @@
       <c r="J95">
         <v>80</v>
       </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
+      <c r="K95" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A96" s="2">
         <v>42137</v>
       </c>
@@ -3927,13 +3774,11 @@
       <c r="J96">
         <v>175</v>
       </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
+      <c r="K96" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97" s="2">
         <v>42138</v>
       </c>
@@ -3964,13 +3809,11 @@
       <c r="J97">
         <v>8827</v>
       </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
+      <c r="K97" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98" s="2">
         <v>42139</v>
       </c>
@@ -4001,13 +3844,11 @@
       <c r="J98">
         <v>180</v>
       </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
+      <c r="K98" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A99" s="2">
         <v>42142</v>
       </c>
@@ -4038,13 +3879,11 @@
       <c r="J99">
         <v>517</v>
       </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
+      <c r="K99" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A100" s="2">
         <v>42143</v>
       </c>
@@ -4075,13 +3914,11 @@
       <c r="J100">
         <v>2210</v>
       </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
+      <c r="K100" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101" s="2">
         <v>42144</v>
       </c>
@@ -4112,13 +3949,11 @@
       <c r="J101">
         <v>30</v>
       </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
+      <c r="K101" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A102" s="2">
         <v>42150</v>
       </c>
@@ -4149,13 +3984,11 @@
       <c r="J102">
         <v>180</v>
       </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
+      <c r="K102" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A103" s="2">
         <v>42151</v>
       </c>
@@ -4186,13 +4019,11 @@
       <c r="J103">
         <v>417.38</v>
       </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
+      <c r="K103" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A104" s="2">
         <v>42153</v>
       </c>
@@ -4223,13 +4054,11 @@
       <c r="J104">
         <v>108</v>
       </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
+      <c r="K104" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A105" s="2">
         <v>42156</v>
       </c>
@@ -4260,13 +4089,11 @@
       <c r="J105">
         <v>11.37</v>
       </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
+      <c r="K105" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A106" s="2">
         <v>42157</v>
       </c>
@@ -4297,13 +4124,11 @@
       <c r="J106">
         <v>7760</v>
       </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
+      <c r="K106" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A107" s="2">
         <v>42158</v>
       </c>
@@ -4334,18 +4159,16 @@
       <c r="J107">
         <v>120</v>
       </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
+      <c r="K107" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A108" s="2">
         <v>42159</v>
       </c>
       <c r="B108">
-        <v>1229.84</v>
+        <v>1229.8399999999999</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -4354,7 +4177,7 @@
         <v>0</v>
       </c>
       <c r="E108">
-        <v>1229.84</v>
+        <v>1229.8399999999999</v>
       </c>
       <c r="F108">
         <v>0</v>
@@ -4369,15 +4192,13 @@
         <v>0</v>
       </c>
       <c r="J108">
-        <v>1229.84</v>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
+        <v>1229.8399999999999</v>
+      </c>
+      <c r="K108" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A109" s="2">
         <v>42160</v>
       </c>
@@ -4408,13 +4229,11 @@
       <c r="J109">
         <v>1690</v>
       </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
+      <c r="K109" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A110" s="2">
         <v>42161</v>
       </c>
@@ -4445,13 +4264,11 @@
       <c r="J110">
         <v>69.75</v>
       </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
+      <c r="K110" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A111" s="2">
         <v>42163</v>
       </c>
@@ -4482,13 +4299,11 @@
       <c r="J111">
         <v>9685.9</v>
       </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
+      <c r="K111" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A112" s="2">
         <v>42164</v>
       </c>
@@ -4519,13 +4334,11 @@
       <c r="J112">
         <v>470</v>
       </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
+      <c r="K112" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A113" s="2">
         <v>42165</v>
       </c>
@@ -4556,13 +4369,11 @@
       <c r="J113">
         <v>377.02</v>
       </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
+      <c r="K113" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A114" s="2">
         <v>42166</v>
       </c>
@@ -4593,13 +4404,11 @@
       <c r="J114">
         <v>210</v>
       </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
+      <c r="K114" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A115" s="2">
         <v>42167</v>
       </c>
@@ -4630,13 +4439,11 @@
       <c r="J115">
         <v>988</v>
       </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
+      <c r="K115" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A116" s="2">
         <v>42170</v>
       </c>
@@ -4667,13 +4474,11 @@
       <c r="J116">
         <v>1319.4</v>
       </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
+      <c r="K116" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A117" s="2">
         <v>42171</v>
       </c>
@@ -4704,13 +4509,11 @@
       <c r="J117">
         <v>802.45</v>
       </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
+      <c r="K117" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A118" s="2">
         <v>42172</v>
       </c>
@@ -4741,13 +4544,11 @@
       <c r="J118">
         <v>43023</v>
       </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
+      <c r="K118" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A119" s="2">
         <v>42173</v>
       </c>
@@ -4778,13 +4579,11 @@
       <c r="J119">
         <v>338.86</v>
       </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
+      <c r="K119" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A120" s="2">
         <v>42174</v>
       </c>
@@ -4815,13 +4614,11 @@
       <c r="J120">
         <v>600</v>
       </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
+      <c r="K120" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A121" s="2">
         <v>42177</v>
       </c>
@@ -4852,13 +4649,11 @@
       <c r="J121">
         <v>488</v>
       </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
+      <c r="K121" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A122" s="2">
         <v>42178</v>
       </c>
@@ -4889,13 +4684,11 @@
       <c r="J122">
         <v>707.79</v>
       </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
+      <c r="K122" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A123" s="2">
         <v>42179</v>
       </c>
@@ -4926,13 +4719,11 @@
       <c r="J123">
         <v>210</v>
       </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
+      <c r="K123" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A124" s="2">
         <v>42180</v>
       </c>
@@ -4946,7 +4737,7 @@
         <v>0</v>
       </c>
       <c r="E124">
-        <v>666.3199999999999</v>
+        <v>666.31999999999994</v>
       </c>
       <c r="F124">
         <v>0</v>
@@ -4961,15 +4752,13 @@
         <v>-216</v>
       </c>
       <c r="J124">
-        <v>450.3199999999999</v>
-      </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
+        <v>450.31999999999988</v>
+      </c>
+      <c r="K124" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A125" s="2">
         <v>42181</v>
       </c>
@@ -5000,13 +4789,11 @@
       <c r="J125">
         <v>148.65</v>
       </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
+      <c r="K125" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A126" s="2">
         <v>42184</v>
       </c>
@@ -5037,13 +4824,11 @@
       <c r="J126">
         <v>810</v>
       </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
+      <c r="K126" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A127" s="2">
         <v>42185</v>
       </c>
@@ -5074,13 +4859,11 @@
       <c r="J127">
         <v>2817.79</v>
       </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
+      <c r="K127" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A128" s="2">
         <v>42186</v>
       </c>
@@ -5111,13 +4894,11 @@
       <c r="J128">
         <v>570</v>
       </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
+      <c r="K128" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A129" s="2">
         <v>42187</v>
       </c>
@@ -5148,13 +4929,11 @@
       <c r="J129">
         <v>270</v>
       </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
+      <c r="K129" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A130" s="2">
         <v>42188</v>
       </c>
@@ -5185,13 +4964,11 @@
       <c r="J130">
         <v>540</v>
       </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
+      <c r="K130" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A131" s="2">
         <v>42191</v>
       </c>
@@ -5222,13 +4999,11 @@
       <c r="J131">
         <v>166.83</v>
       </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
+      <c r="K131" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A132" s="2">
         <v>42192</v>
       </c>
@@ -5259,13 +5034,11 @@
       <c r="J132">
         <v>824.36</v>
       </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
+      <c r="K132" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A133" s="2">
         <v>42193</v>
       </c>
@@ -5296,13 +5069,11 @@
       <c r="J133">
         <v>390</v>
       </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
+      <c r="K133" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A134" s="2">
         <v>42195</v>
       </c>
@@ -5333,13 +5104,11 @@
       <c r="J134">
         <v>5780</v>
       </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
+      <c r="K134" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A135" s="2">
         <v>42199</v>
       </c>
@@ -5370,13 +5139,11 @@
       <c r="J135">
         <v>255</v>
       </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
+      <c r="K135" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A136" s="2">
         <v>42200</v>
       </c>
@@ -5407,13 +5174,11 @@
       <c r="J136">
         <v>560</v>
       </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
+      <c r="K136" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A137" s="2">
         <v>42202</v>
       </c>
@@ -5444,13 +5209,11 @@
       <c r="J137">
         <v>0</v>
       </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
+      <c r="K137" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A138" s="2">
         <v>42205</v>
       </c>
@@ -5481,13 +5244,11 @@
       <c r="J138">
         <v>859</v>
       </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
+      <c r="K138" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A139" s="2">
         <v>42206</v>
       </c>
@@ -5518,13 +5279,11 @@
       <c r="J139">
         <v>60.12</v>
       </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
+      <c r="K139" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A140" s="2">
         <v>42207</v>
       </c>
@@ -5555,13 +5314,11 @@
       <c r="J140">
         <v>7000</v>
       </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
+      <c r="K140" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A141" s="2">
         <v>42208</v>
       </c>
@@ -5592,18 +5349,16 @@
       <c r="J141">
         <v>30</v>
       </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
+      <c r="K141" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A142" s="2">
         <v>42209</v>
       </c>
       <c r="B142">
-        <v>69.90000000000001</v>
+        <v>69.900000000000006</v>
       </c>
       <c r="C142">
         <v>0</v>
@@ -5612,7 +5367,7 @@
         <v>0</v>
       </c>
       <c r="E142">
-        <v>69.90000000000001</v>
+        <v>69.900000000000006</v>
       </c>
       <c r="F142">
         <v>0</v>
@@ -5627,15 +5382,13 @@
         <v>0</v>
       </c>
       <c r="J142">
-        <v>69.90000000000001</v>
-      </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
+        <v>69.900000000000006</v>
+      </c>
+      <c r="K142" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A143" s="2">
         <v>42213</v>
       </c>
@@ -5666,13 +5419,11 @@
       <c r="J143">
         <v>270</v>
       </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
+      <c r="K143" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A144" s="2">
         <v>42214</v>
       </c>
@@ -5703,13 +5454,11 @@
       <c r="J144">
         <v>30</v>
       </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
+      <c r="K144" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A145" s="2">
         <v>42215</v>
       </c>
@@ -5740,13 +5489,11 @@
       <c r="J145">
         <v>2700.06</v>
       </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
+      <c r="K145" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A146" s="2">
         <v>42216</v>
       </c>
@@ -5777,13 +5524,11 @@
       <c r="J146">
         <v>663.85</v>
       </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
+      <c r="K146" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A147" s="2">
         <v>42219</v>
       </c>
@@ -5814,13 +5559,11 @@
       <c r="J147">
         <v>197.44</v>
       </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
+      <c r="K147" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A148" s="2">
         <v>42220</v>
       </c>
@@ -5851,13 +5594,11 @@
       <c r="J148">
         <v>50</v>
       </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
+      <c r="K148" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A149" s="2">
         <v>42221</v>
       </c>
@@ -5888,13 +5629,11 @@
       <c r="J149">
         <v>1148</v>
       </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
+      <c r="K149" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A150" s="2">
         <v>42222</v>
       </c>
@@ -5925,13 +5664,11 @@
       <c r="J150">
         <v>880</v>
       </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
+      <c r="K150" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A151" s="2">
         <v>42223</v>
       </c>
@@ -5962,13 +5699,11 @@
       <c r="J151">
         <v>1985</v>
       </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
+      <c r="K151" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A152" s="2">
         <v>42226</v>
       </c>
@@ -5999,13 +5734,11 @@
       <c r="J152">
         <v>270</v>
       </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
+      <c r="K152" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A153" s="2">
         <v>42227</v>
       </c>
@@ -6036,13 +5769,11 @@
       <c r="J153">
         <v>180</v>
       </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
+      <c r="K153" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A154" s="2">
         <v>42228</v>
       </c>
@@ -6073,13 +5804,11 @@
       <c r="J154">
         <v>210</v>
       </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
+      <c r="K154" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A155" s="2">
         <v>42229</v>
       </c>
@@ -6110,13 +5839,11 @@
       <c r="J155">
         <v>181.12</v>
       </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
+      <c r="K155" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A156" s="2">
         <v>42230</v>
       </c>
@@ -6145,15 +5872,13 @@
         <v>11.46</v>
       </c>
       <c r="J156">
-        <v>702.1600000000001</v>
-      </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
+        <v>702.16000000000008</v>
+      </c>
+      <c r="K156" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A157" s="2">
         <v>42234</v>
       </c>
@@ -6184,13 +5909,11 @@
       <c r="J157">
         <v>2028</v>
       </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
+      <c r="K157" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A158" s="2">
         <v>42235</v>
       </c>
@@ -6221,13 +5944,11 @@
       <c r="J158">
         <v>540</v>
       </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
+      <c r="K158" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A159" s="2">
         <v>42236</v>
       </c>
@@ -6258,13 +5979,11 @@
       <c r="J159">
         <v>300.94</v>
       </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
+      <c r="K159" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A160" s="2">
         <v>42237</v>
       </c>
@@ -6295,13 +6014,11 @@
       <c r="J160">
         <v>5841.15</v>
       </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
+      <c r="K160" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A161" s="2">
         <v>42247</v>
       </c>
@@ -6332,13 +6049,11 @@
       <c r="J161">
         <v>707.75</v>
       </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
+      <c r="K161" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A162" s="2">
         <v>42248</v>
       </c>
@@ -6369,13 +6084,11 @@
       <c r="J162">
         <v>118.14</v>
       </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
+      <c r="K162" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A163" s="2">
         <v>42250</v>
       </c>
@@ -6406,13 +6119,11 @@
       <c r="J163">
         <v>210</v>
       </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
+      <c r="K163" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A164" s="2">
         <v>42251</v>
       </c>
@@ -6443,13 +6154,11 @@
       <c r="J164">
         <v>950</v>
       </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
+      <c r="K164" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A165" s="2">
         <v>42254</v>
       </c>
@@ -6480,13 +6189,11 @@
       <c r="J165">
         <v>-205.34</v>
       </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
+      <c r="K165" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A166" s="2">
         <v>42255</v>
       </c>
@@ -6517,13 +6224,11 @@
       <c r="J166">
         <v>210</v>
       </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
+      <c r="K166" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A167" s="2">
         <v>42256</v>
       </c>
@@ -6554,13 +6259,11 @@
       <c r="J167">
         <v>30</v>
       </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
+      <c r="K167" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A168" s="2">
         <v>42257</v>
       </c>
@@ -6591,13 +6294,11 @@
       <c r="J168">
         <v>84.66</v>
       </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
+      <c r="K168" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A169" s="2">
         <v>42261</v>
       </c>
@@ -6628,13 +6329,11 @@
       <c r="J169">
         <v>154.43</v>
       </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
+      <c r="K169" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="170" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A170" s="2">
         <v>42262</v>
       </c>
@@ -6665,13 +6364,11 @@
       <c r="J170">
         <v>150</v>
       </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
+      <c r="K170" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A171" s="2">
         <v>42263</v>
       </c>
@@ -6702,13 +6399,11 @@
       <c r="J171">
         <v>270</v>
       </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
+      <c r="K171" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A172" s="2">
         <v>42264</v>
       </c>
@@ -6739,13 +6434,11 @@
       <c r="J172">
         <v>213</v>
       </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
+      <c r="K172" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A173" s="2">
         <v>42265</v>
       </c>
@@ -6776,13 +6469,11 @@
       <c r="J173">
         <v>90</v>
       </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
+      <c r="K173" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A174" s="2">
         <v>42268</v>
       </c>
@@ -6813,13 +6504,11 @@
       <c r="J174">
         <v>65.81</v>
       </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
+      <c r="K174" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="175" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A175" s="2">
         <v>42269</v>
       </c>
@@ -6850,13 +6539,11 @@
       <c r="J175">
         <v>150</v>
       </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
+      <c r="K175" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A176" s="2">
         <v>42270</v>
       </c>
@@ -6887,13 +6574,11 @@
       <c r="J176">
         <v>68.7</v>
       </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
+      <c r="K176" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A177" s="2">
         <v>42271</v>
       </c>
@@ -6924,13 +6609,11 @@
       <c r="J177">
         <v>800</v>
       </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
+      <c r="K177" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A178" s="2">
         <v>42272</v>
       </c>
@@ -6961,18 +6644,16 @@
       <c r="J178">
         <v>34.22</v>
       </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
+      <c r="K178" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A179" s="2">
         <v>42275</v>
       </c>
       <c r="B179">
-        <v>938.6799999999999</v>
+        <v>938.68</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -6981,7 +6662,7 @@
         <v>0</v>
       </c>
       <c r="E179">
-        <v>938.6799999999999</v>
+        <v>938.68</v>
       </c>
       <c r="F179">
         <v>0</v>
@@ -6996,15 +6677,13 @@
         <v>0</v>
       </c>
       <c r="J179">
-        <v>938.6799999999999</v>
-      </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
+        <v>938.68</v>
+      </c>
+      <c r="K179" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A180" s="2">
         <v>42276</v>
       </c>
@@ -7035,13 +6714,11 @@
       <c r="J180">
         <v>316.74</v>
       </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
+      <c r="K180" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A181" s="2">
         <v>42277</v>
       </c>
@@ -7072,18 +6749,16 @@
       <c r="J181">
         <v>450</v>
       </c>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
+      <c r="K181" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="182" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A182" s="2">
         <v>42278</v>
       </c>
       <c r="B182">
-        <v>2.24</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="C182">
         <v>0</v>
@@ -7092,7 +6767,7 @@
         <v>0</v>
       </c>
       <c r="E182">
-        <v>2.24</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="F182">
         <v>0</v>
@@ -7107,15 +6782,13 @@
         <v>0</v>
       </c>
       <c r="J182">
-        <v>2.24</v>
-      </c>
-      <c r="K182" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="K182" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A183" s="2">
         <v>42279</v>
       </c>
@@ -7146,13 +6819,11 @@
       <c r="J183">
         <v>270</v>
       </c>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
+      <c r="K183" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A184" s="2">
         <v>42282</v>
       </c>
@@ -7183,13 +6854,11 @@
       <c r="J184">
         <v>1274.74</v>
       </c>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
+      <c r="K184" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A185" s="2">
         <v>42283</v>
       </c>
@@ -7220,13 +6889,11 @@
       <c r="J185">
         <v>524.71</v>
       </c>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
+      <c r="K185" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A186" s="2">
         <v>42284</v>
       </c>
@@ -7257,13 +6924,11 @@
       <c r="J186">
         <v>736.62</v>
       </c>
-      <c r="K186" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
+      <c r="K186" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A187" s="2">
         <v>42285</v>
       </c>
@@ -7294,13 +6959,11 @@
       <c r="J187">
         <v>2144.54</v>
       </c>
-      <c r="K187" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
+      <c r="K187" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A188" s="2">
         <v>42286</v>
       </c>
@@ -7331,18 +6994,16 @@
       <c r="J188">
         <v>328.25</v>
       </c>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
+      <c r="K188" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A189" s="2">
         <v>42291</v>
       </c>
       <c r="B189">
-        <v>147.2</v>
+        <v>147.19999999999999</v>
       </c>
       <c r="C189">
         <v>0</v>
@@ -7351,7 +7012,7 @@
         <v>0</v>
       </c>
       <c r="E189">
-        <v>147.2</v>
+        <v>147.19999999999999</v>
       </c>
       <c r="F189">
         <v>0</v>
@@ -7366,15 +7027,13 @@
         <v>0</v>
       </c>
       <c r="J189">
-        <v>147.2</v>
-      </c>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
+        <v>147.19999999999999</v>
+      </c>
+      <c r="K189" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A190" s="2">
         <v>42292</v>
       </c>
@@ -7405,13 +7064,11 @@
       <c r="J190">
         <v>150</v>
       </c>
-      <c r="K190" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
+      <c r="K190" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="191" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A191" s="2">
         <v>42293</v>
       </c>
@@ -7442,13 +7099,11 @@
       <c r="J191">
         <v>206.3</v>
       </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
+      <c r="K191" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A192" s="2">
         <v>42296</v>
       </c>
@@ -7479,13 +7134,11 @@
       <c r="J192">
         <v>370</v>
       </c>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
+      <c r="K192" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="193" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A193" s="2">
         <v>42297</v>
       </c>
@@ -7516,13 +7169,11 @@
       <c r="J193">
         <v>207.42</v>
       </c>
-      <c r="K193" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
+      <c r="K193" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="194" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A194" s="2">
         <v>42298</v>
       </c>
@@ -7553,13 +7204,11 @@
       <c r="J194">
         <v>616</v>
       </c>
-      <c r="K194" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
+      <c r="K194" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="195" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A195" s="2">
         <v>42299</v>
       </c>
@@ -7590,18 +7239,16 @@
       <c r="J195">
         <v>800</v>
       </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
+      <c r="K195" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="196" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A196" s="2">
         <v>42300</v>
       </c>
       <c r="B196">
-        <v>266.16</v>
+        <v>266.16000000000003</v>
       </c>
       <c r="C196">
         <v>0</v>
@@ -7627,13 +7274,11 @@
       <c r="J196">
         <v>116.16</v>
       </c>
-      <c r="K196" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
+      <c r="K196" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="197" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A197" s="2">
         <v>42303</v>
       </c>
@@ -7664,13 +7309,11 @@
       <c r="J197">
         <v>230.94</v>
       </c>
-      <c r="K197" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
+      <c r="K197" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="198" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A198" s="2">
         <v>42304</v>
       </c>
@@ -7701,13 +7344,11 @@
       <c r="J198">
         <v>1163.08</v>
       </c>
-      <c r="K198" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
+      <c r="K198" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="199" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A199" s="2">
         <v>42305</v>
       </c>
@@ -7738,13 +7379,11 @@
       <c r="J199">
         <v>10</v>
       </c>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
+      <c r="K199" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="200" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A200" s="2">
         <v>42306</v>
       </c>
@@ -7775,13 +7414,11 @@
       <c r="J200">
         <v>694.24</v>
       </c>
-      <c r="K200" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
+      <c r="K200" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="201" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A201" s="2">
         <v>42307</v>
       </c>
@@ -7812,13 +7449,11 @@
       <c r="J201">
         <v>194.42</v>
       </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
+      <c r="K201" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="202" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A202" s="2">
         <v>42310</v>
       </c>
@@ -7849,13 +7484,11 @@
       <c r="J202">
         <v>510</v>
       </c>
-      <c r="K202" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
+      <c r="K202" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="203" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A203" s="2">
         <v>42311</v>
       </c>
@@ -7886,13 +7519,11 @@
       <c r="J203">
         <v>517.14</v>
       </c>
-      <c r="K203" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
+      <c r="K203" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="204" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A204" s="2">
         <v>42312</v>
       </c>
@@ -7923,13 +7554,11 @@
       <c r="J204">
         <v>180</v>
       </c>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
+      <c r="K204" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="205" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A205" s="2">
         <v>42313</v>
       </c>
@@ -7960,13 +7589,11 @@
       <c r="J205">
         <v>2180.59</v>
       </c>
-      <c r="K205" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
+      <c r="K205" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="206" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A206" s="2">
         <v>42314</v>
       </c>
@@ -7997,13 +7624,11 @@
       <c r="J206">
         <v>874</v>
       </c>
-      <c r="K206" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
+      <c r="K206" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="207" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A207" s="2">
         <v>42317</v>
       </c>
@@ -8034,13 +7659,11 @@
       <c r="J207">
         <v>369</v>
       </c>
-      <c r="K207" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
+      <c r="K207" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="208" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A208" s="2">
         <v>42318</v>
       </c>
@@ -8071,13 +7694,11 @@
       <c r="J208">
         <v>1388</v>
       </c>
-      <c r="K208" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
+      <c r="K208" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="209" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A209" s="2">
         <v>42319</v>
       </c>
@@ -8108,13 +7729,11 @@
       <c r="J209">
         <v>1367.72</v>
       </c>
-      <c r="K209" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
+      <c r="K209" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="210" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A210" s="2">
         <v>42320</v>
       </c>
@@ -8145,13 +7764,11 @@
       <c r="J210">
         <v>1754.86</v>
       </c>
-      <c r="K210" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
+      <c r="K210" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="211" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A211" s="2">
         <v>42321</v>
       </c>
@@ -8182,13 +7799,11 @@
       <c r="J211">
         <v>1100</v>
       </c>
-      <c r="K211" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
+      <c r="K211" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="212" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A212" s="2">
         <v>42324</v>
       </c>
@@ -8202,7 +7817,7 @@
         <v>0</v>
       </c>
       <c r="E212">
-        <v>518.92</v>
+        <v>518.91999999999996</v>
       </c>
       <c r="F212">
         <v>0</v>
@@ -8217,15 +7832,13 @@
         <v>0</v>
       </c>
       <c r="J212">
-        <v>518.92</v>
-      </c>
-      <c r="K212" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
+        <v>518.91999999999996</v>
+      </c>
+      <c r="K212" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="213" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A213" s="2">
         <v>42325</v>
       </c>
@@ -8256,13 +7869,11 @@
       <c r="J213">
         <v>2015.25</v>
       </c>
-      <c r="K213" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
+      <c r="K213" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="214" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A214" s="2">
         <v>42326</v>
       </c>
@@ -8293,13 +7904,11 @@
       <c r="J214">
         <v>358.78</v>
       </c>
-      <c r="K214" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
+      <c r="K214" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="215" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A215" s="2">
         <v>42327</v>
       </c>
@@ -8330,13 +7939,11 @@
       <c r="J215">
         <v>35.5</v>
       </c>
-      <c r="K215" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
+      <c r="K215" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="216" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A216" s="2">
         <v>42328</v>
       </c>
@@ -8367,13 +7974,11 @@
       <c r="J216">
         <v>1440</v>
       </c>
-      <c r="K216" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
+      <c r="K216" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="217" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A217" s="2">
         <v>42331</v>
       </c>
@@ -8404,13 +8009,11 @@
       <c r="J217">
         <v>60</v>
       </c>
-      <c r="K217" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
+      <c r="K217" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="218" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A218" s="2">
         <v>42332</v>
       </c>
@@ -8441,13 +8044,11 @@
       <c r="J218">
         <v>2337.84</v>
       </c>
-      <c r="K218" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
+      <c r="K218" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="219" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A219" s="2">
         <v>42333</v>
       </c>
@@ -8478,18 +8079,16 @@
       <c r="J219">
         <v>1507.32</v>
       </c>
-      <c r="K219" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
+      <c r="K219" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="220" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A220" s="2">
         <v>42334</v>
       </c>
       <c r="B220">
-        <v>645.05</v>
+        <v>645.04999999999995</v>
       </c>
       <c r="C220">
         <v>27.52</v>
@@ -8498,7 +8097,7 @@
         <v>0</v>
       </c>
       <c r="E220">
-        <v>672.5699999999999</v>
+        <v>672.56999999999994</v>
       </c>
       <c r="F220">
         <v>0</v>
@@ -8513,15 +8112,13 @@
         <v>0</v>
       </c>
       <c r="J220">
-        <v>672.5699999999999</v>
-      </c>
-      <c r="K220" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
+        <v>672.56999999999994</v>
+      </c>
+      <c r="K220" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="221" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A221" s="2">
         <v>42338</v>
       </c>
@@ -8552,18 +8149,16 @@
       <c r="J221">
         <v>656.5</v>
       </c>
-      <c r="K221" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
+      <c r="K221" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="222" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A222" s="2">
         <v>42339</v>
       </c>
       <c r="B222">
-        <v>1179.14</v>
+        <v>1179.1400000000001</v>
       </c>
       <c r="C222">
         <v>0</v>
@@ -8572,7 +8167,7 @@
         <v>0</v>
       </c>
       <c r="E222">
-        <v>1179.14</v>
+        <v>1179.1400000000001</v>
       </c>
       <c r="F222">
         <v>0</v>
@@ -8587,15 +8182,13 @@
         <v>0</v>
       </c>
       <c r="J222">
-        <v>1179.14</v>
-      </c>
-      <c r="K222" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
+        <v>1179.1400000000001</v>
+      </c>
+      <c r="K222" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="223" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A223" s="2">
         <v>42340</v>
       </c>
@@ -8626,13 +8219,11 @@
       <c r="J223">
         <v>2530</v>
       </c>
-      <c r="K223" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
+      <c r="K223" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="224" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A224" s="2">
         <v>42341</v>
       </c>
@@ -8663,13 +8254,11 @@
       <c r="J224">
         <v>799.92</v>
       </c>
-      <c r="K224" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
+      <c r="K224" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="225" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A225" s="2">
         <v>42342</v>
       </c>
@@ -8700,18 +8289,16 @@
       <c r="J225">
         <v>2066.92</v>
       </c>
-      <c r="K225" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
+      <c r="K225" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="226" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A226" s="2">
         <v>42343</v>
       </c>
       <c r="B226">
-        <v>67.94999999999999</v>
+        <v>67.949999999999989</v>
       </c>
       <c r="C226">
         <v>0</v>
@@ -8720,7 +8307,7 @@
         <v>0</v>
       </c>
       <c r="E226">
-        <v>67.94999999999999</v>
+        <v>67.949999999999989</v>
       </c>
       <c r="F226">
         <v>0</v>
@@ -8735,15 +8322,13 @@
         <v>0</v>
       </c>
       <c r="J226">
-        <v>67.94999999999999</v>
-      </c>
-      <c r="K226" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
+        <v>67.949999999999989</v>
+      </c>
+      <c r="K226" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="227" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A227" s="2">
         <v>42347</v>
       </c>
@@ -8774,13 +8359,11 @@
       <c r="J227">
         <v>5105.16</v>
       </c>
-      <c r="K227" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
+      <c r="K227" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="228" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A228" s="2">
         <v>42348</v>
       </c>
@@ -8811,13 +8394,11 @@
       <c r="J228">
         <v>12273.98</v>
       </c>
-      <c r="K228" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
+      <c r="K228" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="229" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A229" s="2">
         <v>42349</v>
       </c>
@@ -8848,13 +8429,11 @@
       <c r="J229">
         <v>17450</v>
       </c>
-      <c r="K229" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
+      <c r="K229" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="230" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A230" s="2">
         <v>42352</v>
       </c>
@@ -8885,13 +8464,11 @@
       <c r="J230">
         <v>28752.38</v>
       </c>
-      <c r="K230" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
+      <c r="K230" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="231" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A231" s="2">
         <v>42353</v>
       </c>
@@ -8922,13 +8499,11 @@
       <c r="J231">
         <v>17061.82</v>
       </c>
-      <c r="K231" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
+      <c r="K231" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="232" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A232" s="2">
         <v>42354</v>
       </c>
@@ -8959,13 +8534,11 @@
       <c r="J232">
         <v>48444.55</v>
       </c>
-      <c r="K232" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
+      <c r="K232" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="233" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A233" s="2">
         <v>42355</v>
       </c>
@@ -8979,7 +8552,7 @@
         <v>200</v>
       </c>
       <c r="E233">
-        <v>35838.08</v>
+        <v>35838.080000000002</v>
       </c>
       <c r="F233">
         <v>1150</v>
@@ -8994,15 +8567,13 @@
         <v>1150</v>
       </c>
       <c r="J233">
-        <v>36988.08</v>
-      </c>
-      <c r="K233" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
+        <v>36988.080000000002</v>
+      </c>
+      <c r="K233" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="234" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A234" s="2">
         <v>42356</v>
       </c>
@@ -9033,13 +8604,11 @@
       <c r="J234">
         <v>54442.82</v>
       </c>
-      <c r="K234" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
+      <c r="K234" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="235" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A235" s="2">
         <v>42357</v>
       </c>
@@ -9070,13 +8639,11 @@
       <c r="J235">
         <v>240</v>
       </c>
-      <c r="K235" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
+      <c r="K235" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="236" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A236" s="2">
         <v>42359</v>
       </c>
@@ -9107,13 +8674,11 @@
       <c r="J236">
         <v>54030.47</v>
       </c>
-      <c r="K236" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
+      <c r="K236" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="237" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A237" s="2">
         <v>42360</v>
       </c>
@@ -9144,18 +8709,16 @@
       <c r="J237">
         <v>52522.71</v>
       </c>
-      <c r="K237" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
+      <c r="K237" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="238" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A238" s="2">
         <v>42361</v>
       </c>
       <c r="B238">
-        <v>20936.83</v>
+        <v>20936.830000000002</v>
       </c>
       <c r="C238">
         <v>720</v>
@@ -9181,13 +8744,11 @@
       <c r="J238">
         <v>22056.83</v>
       </c>
-      <c r="K238" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
+      <c r="K238" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="239" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A239" s="2">
         <v>42362</v>
       </c>
@@ -9218,13 +8779,11 @@
       <c r="J239">
         <v>5810</v>
       </c>
-      <c r="K239" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
+      <c r="K239" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="240" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A240" s="2">
         <v>42364</v>
       </c>
@@ -9255,13 +8814,11 @@
       <c r="J240">
         <v>330</v>
       </c>
-      <c r="K240" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
+      <c r="K240" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="241" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A241" s="2">
         <v>42366</v>
       </c>
@@ -9292,13 +8849,11 @@
       <c r="J241">
         <v>58684.87</v>
       </c>
-      <c r="K241" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
+      <c r="K241" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="242" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A242" s="2">
         <v>42367</v>
       </c>
@@ -9329,13 +8884,11 @@
       <c r="J242">
         <v>60001.16</v>
       </c>
-      <c r="K242" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
+      <c r="K242" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="243" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A243" s="2">
         <v>42368</v>
       </c>
@@ -9366,13 +8919,11 @@
       <c r="J243">
         <v>43635.19</v>
       </c>
-      <c r="K243" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
+      <c r="K243" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="244" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A244" s="2">
         <v>42369</v>
       </c>
@@ -9403,307 +8954,11 @@
       <c r="J244">
         <v>300</v>
       </c>
-      <c r="K244" t="inlineStr">
-        <is>
-          <t>CEBADA</t>
-        </is>
+      <c r="K244" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100D6CA5EAACE9DA04D9E421A617A76D009" ma:contentTypeVersion="19" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="bac5de4a034fee97af64ba5a2822cd53">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="77131357-5c03-45fa-a80b-b9111bb46cb1" xmlns:ns3="d3f11db4-a96c-41b4-b8ec-902c72f52048" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="027d3429df443898fbbc0b888682b5bf" ns2:_="" ns3:_="">
-    <xsd:import namespace="77131357-5c03-45fa-a80b-b9111bb46cb1"/>
-    <xsd:import namespace="d3f11db4-a96c-41b4-b8ec-902c72f52048"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:_Flow_SignoffStatus" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="77131357-5c03-45fa-a80b-b9111bb46cb1" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="10" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="11" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="14" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="15" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="17" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="_Flow_SignoffStatus" ma:index="20" nillable="true" ma:displayName="Estado de aprobación" ma:internalName="Estado_x0020_de_x0020_aprobaci_x00f3_n">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="21" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="23" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="6ab20cb4-9c0f-41d2-89f3-02c382a657d6" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="25" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="26" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="d3f11db4-a96c-41b4-b8ec-902c72f52048" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="18" nillable="true" ma:displayName="Compartido con" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="19" nillable="true" ma:displayName="Detalles de uso compartido" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="24" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ac6aff7b-77d9-4645-af3f-7b0008d975fa}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="d3f11db4-a96c-41b4-b8ec-902c72f52048">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="77131357-5c03-45fa-a80b-b9111bb46cb1" xsi:nil="true"/>
-    <TaxCatchAll xmlns="d3f11db4-a96c-41b4-b8ec-902c72f52048" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="77131357-5c03-45fa-a80b-b9111bb46cb1">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11941668-4833-4AA6-BAE2-76305FC99647}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19C2E3AE-15E8-4BB2-8FC0-F2762B2D571C}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9709AA14-CFE6-439E-8FF8-04F52F4659D3}"/>
 </file>
--- a/Datos limpios/Pricing diario/2015/Cebada.xlsx
+++ b/Datos limpios/Pricing diario/2015/Cebada.xlsx
@@ -1,71 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5528ac80b6f1b5d4/Documents/Maestria en Ciencia de Datos/1. Primer semestre/Análisis inteligente de datos/trabajo-final-belenmaldonado1/Datos limpios/Pricing diario/2015/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="11_AB635DDC8F79A8536E3CA493EA7BD2724ACE2D1E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB3D9E24-699B-4992-982B-604C44E75477}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="12">
-  <si>
-    <t>FECHA_OPERACION</t>
-  </si>
-  <si>
-    <t>CONTRATO</t>
-  </si>
-  <si>
-    <t>CONTRATO_RECTIFICACION</t>
-  </si>
-  <si>
-    <t>CONTRATO_ANULACION</t>
-  </si>
-  <si>
-    <t>CONTRATO_PRECIO_HECHO</t>
-  </si>
-  <si>
-    <t>FIJACION</t>
-  </si>
-  <si>
-    <t>FIJACION_RECTIFICACION</t>
-  </si>
-  <si>
-    <t>FIJACION_ANULACION</t>
-  </si>
-  <si>
-    <t>FIJACIONES</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>PRODUCTO</t>
-  </si>
-  <si>
-    <t>CEBADA</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -114,21 +67,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -136,37 +81,37 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -200,7 +145,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -235,10 +179,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -411,49 +354,71 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K244"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20.6640625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>FECHA_OPERACION</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>CONTRATO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>CONTRATO_RECTIFICACION</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>CONTRATO_ANULACION</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>CONTRATO_PRECIO_HECHO</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>FIJACION</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>FIJACION_RECTIFICACION</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>FIJACION_ANULACION</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>FIJACIONES</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>PRODUCTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="2">
         <v>42006</v>
       </c>
@@ -484,11 +449,13 @@
       <c r="J2">
         <v>630</v>
       </c>
-      <c r="K2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="2">
         <v>42009</v>
       </c>
@@ -519,11 +486,13 @@
       <c r="J3">
         <v>2246</v>
       </c>
-      <c r="K3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="2">
         <v>42010</v>
       </c>
@@ -554,11 +523,13 @@
       <c r="J4">
         <v>4096.58</v>
       </c>
-      <c r="K4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" s="2">
         <v>42011</v>
       </c>
@@ -589,11 +560,13 @@
       <c r="J5">
         <v>1230</v>
       </c>
-      <c r="K5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" s="2">
         <v>42012</v>
       </c>
@@ -624,11 +597,13 @@
       <c r="J6">
         <v>3510</v>
       </c>
-      <c r="K6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" s="2">
         <v>42013</v>
       </c>
@@ -659,11 +634,13 @@
       <c r="J7">
         <v>4498</v>
       </c>
-      <c r="K7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" s="2">
         <v>42016</v>
       </c>
@@ -694,11 +671,13 @@
       <c r="J8">
         <v>3364</v>
       </c>
-      <c r="K8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" s="2">
         <v>42017</v>
       </c>
@@ -729,11 +708,13 @@
       <c r="J9">
         <v>31608</v>
       </c>
-      <c r="K9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" s="2">
         <v>42018</v>
       </c>
@@ -764,11 +745,13 @@
       <c r="J10">
         <v>4915.46</v>
       </c>
-      <c r="K10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" s="2">
         <v>42019</v>
       </c>
@@ -799,11 +782,13 @@
       <c r="J11">
         <v>6430</v>
       </c>
-      <c r="K11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" s="2">
         <v>42020</v>
       </c>
@@ -834,11 +819,13 @@
       <c r="J12">
         <v>7305</v>
       </c>
-      <c r="K12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" s="2">
         <v>42023</v>
       </c>
@@ -869,11 +856,13 @@
       <c r="J13">
         <v>2900</v>
       </c>
-      <c r="K13" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" s="2">
         <v>42024</v>
       </c>
@@ -904,11 +893,13 @@
       <c r="J14">
         <v>4100</v>
       </c>
-      <c r="K14" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15" s="2">
         <v>42025</v>
       </c>
@@ -939,11 +930,13 @@
       <c r="J15">
         <v>1653</v>
       </c>
-      <c r="K15" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16" s="2">
         <v>42026</v>
       </c>
@@ -974,16 +967,18 @@
       <c r="J16">
         <v>5335</v>
       </c>
-      <c r="K16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17" s="2">
         <v>42027</v>
       </c>
       <c r="B17">
-        <v>8621.2199999999993</v>
+        <v>8621.219999999999</v>
       </c>
       <c r="C17">
         <v>1080</v>
@@ -992,7 +987,7 @@
         <v>0</v>
       </c>
       <c r="E17">
-        <v>9701.2199999999993</v>
+        <v>9701.219999999999</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1007,13 +1002,15 @@
         <v>0</v>
       </c>
       <c r="J17">
-        <v>9701.2199999999993</v>
-      </c>
-      <c r="K17" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+        <v>9701.219999999999</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18" s="2">
         <v>42030</v>
       </c>
@@ -1044,11 +1041,13 @@
       <c r="J18">
         <v>16269.6</v>
       </c>
-      <c r="K18" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19" s="2">
         <v>42031</v>
       </c>
@@ -1079,11 +1078,13 @@
       <c r="J19">
         <v>13246.24</v>
       </c>
-      <c r="K19" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
       <c r="A20" s="2">
         <v>42032</v>
       </c>
@@ -1114,11 +1115,13 @@
       <c r="J20">
         <v>13594.38</v>
       </c>
-      <c r="K20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
       <c r="A21" s="2">
         <v>42033</v>
       </c>
@@ -1149,11 +1152,13 @@
       <c r="J21">
         <v>28558.02</v>
       </c>
-      <c r="K21" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
       <c r="A22" s="2">
         <v>42034</v>
       </c>
@@ -1184,11 +1189,13 @@
       <c r="J22">
         <v>41168</v>
       </c>
-      <c r="K22" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
       <c r="A23" s="2">
         <v>42035</v>
       </c>
@@ -1217,13 +1224,15 @@
         <v>44.6</v>
       </c>
       <c r="J23">
-        <v>1034.5999999999999</v>
-      </c>
-      <c r="K23" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+        <v>1034.6</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
       <c r="A24" s="2">
         <v>42036</v>
       </c>
@@ -1254,11 +1263,13 @@
       <c r="J24">
         <v>199.17</v>
       </c>
-      <c r="K24" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
       <c r="A25" s="2">
         <v>42037</v>
       </c>
@@ -1289,16 +1300,18 @@
       <c r="J25">
         <v>11200.85</v>
       </c>
-      <c r="K25" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
       <c r="A26" s="2">
         <v>42038</v>
       </c>
       <c r="B26">
-        <v>8198.0300000000007</v>
+        <v>8198.030000000001</v>
       </c>
       <c r="C26">
         <v>60</v>
@@ -1307,7 +1320,7 @@
         <v>1610</v>
       </c>
       <c r="E26">
-        <v>6648.0300000000007</v>
+        <v>6648.030000000001</v>
       </c>
       <c r="F26">
         <v>60</v>
@@ -1322,13 +1335,15 @@
         <v>60</v>
       </c>
       <c r="J26">
-        <v>6708.0300000000007</v>
-      </c>
-      <c r="K26" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6708.030000000001</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
       <c r="A27" s="2">
         <v>42039</v>
       </c>
@@ -1359,11 +1374,13 @@
       <c r="J27">
         <v>11764.9</v>
       </c>
-      <c r="K27" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
       <c r="A28" s="2">
         <v>42040</v>
       </c>
@@ -1394,11 +1411,13 @@
       <c r="J28">
         <v>3779.05</v>
       </c>
-      <c r="K28" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
       <c r="A29" s="2">
         <v>42041</v>
       </c>
@@ -1429,11 +1448,13 @@
       <c r="J29">
         <v>7983.95</v>
       </c>
-      <c r="K29" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
       <c r="A30" s="2">
         <v>42042</v>
       </c>
@@ -1464,11 +1485,13 @@
       <c r="J30">
         <v>28</v>
       </c>
-      <c r="K30" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
       <c r="A31" s="2">
         <v>42044</v>
       </c>
@@ -1499,11 +1522,13 @@
       <c r="J31">
         <v>3646.63</v>
       </c>
-      <c r="K31" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
       <c r="A32" s="2">
         <v>42045</v>
       </c>
@@ -1534,11 +1559,13 @@
       <c r="J32">
         <v>7588.35</v>
       </c>
-      <c r="K32" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
       <c r="A33" s="2">
         <v>42046</v>
       </c>
@@ -1552,7 +1579,7 @@
         <v>0</v>
       </c>
       <c r="E33">
-        <v>4127.9799999999996</v>
+        <v>4127.98</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -1567,13 +1594,15 @@
         <v>0</v>
       </c>
       <c r="J33">
-        <v>4127.9799999999996</v>
-      </c>
-      <c r="K33" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+        <v>4127.98</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
       <c r="A34" s="2">
         <v>42047</v>
       </c>
@@ -1604,11 +1633,13 @@
       <c r="J34">
         <v>12347.34</v>
       </c>
-      <c r="K34" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
       <c r="A35" s="2">
         <v>42048</v>
       </c>
@@ -1622,7 +1653,7 @@
         <v>1777.94</v>
       </c>
       <c r="E35">
-        <v>18305.650000000001</v>
+        <v>18305.65</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -1637,18 +1668,20 @@
         <v>0</v>
       </c>
       <c r="J35">
-        <v>18305.650000000001</v>
-      </c>
-      <c r="K35" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+        <v>18305.65</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
       <c r="A36" s="2">
         <v>42049</v>
       </c>
       <c r="B36">
-        <v>946.57999999999993</v>
+        <v>946.5799999999999</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -1657,7 +1690,7 @@
         <v>0</v>
       </c>
       <c r="E36">
-        <v>946.57999999999993</v>
+        <v>946.5799999999999</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -1672,13 +1705,15 @@
         <v>0</v>
       </c>
       <c r="J36">
-        <v>946.57999999999993</v>
-      </c>
-      <c r="K36" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+        <v>946.5799999999999</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
       <c r="A37" s="2">
         <v>42052</v>
       </c>
@@ -1709,11 +1744,13 @@
       <c r="J37">
         <v>6618.07</v>
       </c>
-      <c r="K37" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
       <c r="A38" s="2">
         <v>42053</v>
       </c>
@@ -1744,22 +1781,24 @@
       <c r="J38">
         <v>3108</v>
       </c>
-      <c r="K38" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
       <c r="A39" s="2">
         <v>42054</v>
       </c>
       <c r="B39">
-        <v>10394.219999999999</v>
+        <v>10394.22</v>
       </c>
       <c r="C39">
         <v>862.24</v>
       </c>
       <c r="D39">
-        <v>839.31</v>
+        <v>839.3099999999999</v>
       </c>
       <c r="E39">
         <v>10417.15</v>
@@ -1779,11 +1818,13 @@
       <c r="J39">
         <v>10717.15</v>
       </c>
-      <c r="K39" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
       <c r="A40" s="2">
         <v>42055</v>
       </c>
@@ -1814,11 +1855,13 @@
       <c r="J40">
         <v>8191.25</v>
       </c>
-      <c r="K40" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
       <c r="A41" s="2">
         <v>42056</v>
       </c>
@@ -1826,13 +1869,13 @@
         <v>30</v>
       </c>
       <c r="C41">
-        <v>285.54000000000002</v>
+        <v>285.54</v>
       </c>
       <c r="D41">
         <v>0</v>
       </c>
       <c r="E41">
-        <v>315.54000000000002</v>
+        <v>315.54</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -1847,13 +1890,15 @@
         <v>0</v>
       </c>
       <c r="J41">
-        <v>315.54000000000002</v>
-      </c>
-      <c r="K41" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+        <v>315.54</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
       <c r="A42" s="2">
         <v>42058</v>
       </c>
@@ -1884,11 +1929,13 @@
       <c r="J42">
         <v>4857.66</v>
       </c>
-      <c r="K42" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
       <c r="A43" s="2">
         <v>42059</v>
       </c>
@@ -1919,11 +1966,13 @@
       <c r="J43">
         <v>6458.25</v>
       </c>
-      <c r="K43" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
       <c r="A44" s="2">
         <v>42060</v>
       </c>
@@ -1954,11 +2003,13 @@
       <c r="J44">
         <v>2356.52</v>
       </c>
-      <c r="K44" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
       <c r="A45" s="2">
         <v>42061</v>
       </c>
@@ -1989,11 +2040,13 @@
       <c r="J45">
         <v>6505.81</v>
       </c>
-      <c r="K45" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
       <c r="A46" s="2">
         <v>42062</v>
       </c>
@@ -2024,11 +2077,13 @@
       <c r="J46">
         <v>2640.04</v>
       </c>
-      <c r="K46" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
       <c r="A47" s="2">
         <v>42065</v>
       </c>
@@ -2059,11 +2114,13 @@
       <c r="J47">
         <v>2590</v>
       </c>
-      <c r="K47" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
       <c r="A48" s="2">
         <v>42066</v>
       </c>
@@ -2094,11 +2151,13 @@
       <c r="J48">
         <v>1183.42</v>
       </c>
-      <c r="K48" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
       <c r="A49" s="2">
         <v>42067</v>
       </c>
@@ -2109,7 +2168,7 @@
         <v>124.44</v>
       </c>
       <c r="D49">
-        <v>55.239999999999988</v>
+        <v>55.23999999999999</v>
       </c>
       <c r="E49">
         <v>3346.11</v>
@@ -2129,11 +2188,13 @@
       <c r="J49">
         <v>3346.11</v>
       </c>
-      <c r="K49" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
       <c r="A50" s="2">
         <v>42068</v>
       </c>
@@ -2164,11 +2225,13 @@
       <c r="J50">
         <v>1497.27</v>
       </c>
-      <c r="K50" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
       <c r="A51" s="2">
         <v>42069</v>
       </c>
@@ -2199,11 +2262,13 @@
       <c r="J51">
         <v>3728.36</v>
       </c>
-      <c r="K51" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
       <c r="A52" s="2">
         <v>42072</v>
       </c>
@@ -2234,11 +2299,13 @@
       <c r="J52">
         <v>3754.68</v>
       </c>
-      <c r="K52" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
       <c r="A53" s="2">
         <v>42073</v>
       </c>
@@ -2269,11 +2336,13 @@
       <c r="J53">
         <v>4418</v>
       </c>
-      <c r="K53" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
       <c r="A54" s="2">
         <v>42074</v>
       </c>
@@ -2304,11 +2373,13 @@
       <c r="J54">
         <v>965</v>
       </c>
-      <c r="K54" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
       <c r="A55" s="2">
         <v>42075</v>
       </c>
@@ -2339,11 +2410,13 @@
       <c r="J55">
         <v>1636</v>
       </c>
-      <c r="K55" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
       <c r="A56" s="2">
         <v>42076</v>
       </c>
@@ -2374,11 +2447,13 @@
       <c r="J56">
         <v>610</v>
       </c>
-      <c r="K56" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
       <c r="A57" s="2">
         <v>42079</v>
       </c>
@@ -2409,11 +2484,13 @@
       <c r="J57">
         <v>3125.02</v>
       </c>
-      <c r="K57" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
       <c r="A58" s="2">
         <v>42080</v>
       </c>
@@ -2444,11 +2521,13 @@
       <c r="J58">
         <v>3067.06</v>
       </c>
-      <c r="K58" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
       <c r="A59" s="2">
         <v>42081</v>
       </c>
@@ -2479,16 +2558,18 @@
       <c r="J59">
         <v>1137.01</v>
       </c>
-      <c r="K59" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
       <c r="A60" s="2">
         <v>42082</v>
       </c>
       <c r="B60">
-        <v>8900.44</v>
+        <v>8900.440000000001</v>
       </c>
       <c r="C60">
         <v>605.62</v>
@@ -2497,7 +2578,7 @@
         <v>0</v>
       </c>
       <c r="E60">
-        <v>9506.0600000000013</v>
+        <v>9506.060000000001</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -2512,13 +2593,15 @@
         <v>0</v>
       </c>
       <c r="J60">
-        <v>9506.0600000000013</v>
-      </c>
-      <c r="K60" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+        <v>9506.060000000001</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
       <c r="A61" s="2">
         <v>42083</v>
       </c>
@@ -2549,11 +2632,13 @@
       <c r="J61">
         <v>1476.83</v>
       </c>
-      <c r="K61" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
       <c r="A62" s="2">
         <v>42084</v>
       </c>
@@ -2584,11 +2669,13 @@
       <c r="J62">
         <v>767.24</v>
       </c>
-      <c r="K62" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
       <c r="A63" s="2">
         <v>42088</v>
       </c>
@@ -2619,11 +2706,13 @@
       <c r="J63">
         <v>1431.55</v>
       </c>
-      <c r="K63" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
       <c r="A64" s="2">
         <v>42089</v>
       </c>
@@ -2654,11 +2743,13 @@
       <c r="J64">
         <v>2041.62</v>
       </c>
-      <c r="K64" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
       <c r="A65" s="2">
         <v>42090</v>
       </c>
@@ -2689,11 +2780,13 @@
       <c r="J65">
         <v>687</v>
       </c>
-      <c r="K65" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
       <c r="A66" s="2">
         <v>42091</v>
       </c>
@@ -2724,11 +2817,13 @@
       <c r="J66">
         <v>62.17</v>
       </c>
-      <c r="K66" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
       <c r="A67" s="2">
         <v>42093</v>
       </c>
@@ -2759,11 +2854,13 @@
       <c r="J67">
         <v>1268</v>
       </c>
-      <c r="K67" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
       <c r="A68" s="2">
         <v>42094</v>
       </c>
@@ -2794,11 +2891,13 @@
       <c r="J68">
         <v>560</v>
       </c>
-      <c r="K68" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
       <c r="A69" s="2">
         <v>42095</v>
       </c>
@@ -2829,11 +2928,13 @@
       <c r="J69">
         <v>1064</v>
       </c>
-      <c r="K69" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
       <c r="A70" s="2">
         <v>42100</v>
       </c>
@@ -2864,11 +2965,13 @@
       <c r="J70">
         <v>436</v>
       </c>
-      <c r="K70" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
       <c r="A71" s="2">
         <v>42101</v>
       </c>
@@ -2899,11 +3002,13 @@
       <c r="J71">
         <v>2522.29</v>
       </c>
-      <c r="K71" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
       <c r="A72" s="2">
         <v>42102</v>
       </c>
@@ -2934,11 +3039,13 @@
       <c r="J72">
         <v>710</v>
       </c>
-      <c r="K72" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
       <c r="A73" s="2">
         <v>42103</v>
       </c>
@@ -2969,11 +3076,13 @@
       <c r="J73">
         <v>1095</v>
       </c>
-      <c r="K73" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
       <c r="A74" s="2">
         <v>42104</v>
       </c>
@@ -3004,11 +3113,13 @@
       <c r="J74">
         <v>328</v>
       </c>
-      <c r="K74" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
       <c r="A75" s="2">
         <v>42107</v>
       </c>
@@ -3039,11 +3150,13 @@
       <c r="J75">
         <v>120</v>
       </c>
-      <c r="K75" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
       <c r="A76" s="2">
         <v>42108</v>
       </c>
@@ -3074,11 +3187,13 @@
       <c r="J76">
         <v>2187</v>
       </c>
-      <c r="K76" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
       <c r="A77" s="2">
         <v>42109</v>
       </c>
@@ -3109,11 +3224,13 @@
       <c r="J77">
         <v>892.9</v>
       </c>
-      <c r="K77" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
       <c r="A78" s="2">
         <v>42110</v>
       </c>
@@ -3127,7 +3244,7 @@
         <v>0</v>
       </c>
       <c r="E78">
-        <v>536.05999999999995</v>
+        <v>536.0599999999999</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -3142,13 +3259,15 @@
         <v>0</v>
       </c>
       <c r="J78">
-        <v>536.05999999999995</v>
-      </c>
-      <c r="K78" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+        <v>536.0599999999999</v>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
       <c r="A79" s="2">
         <v>42111</v>
       </c>
@@ -3179,11 +3298,13 @@
       <c r="J79">
         <v>442</v>
       </c>
-      <c r="K79" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
       <c r="A80" s="2">
         <v>42114</v>
       </c>
@@ -3214,11 +3335,13 @@
       <c r="J80">
         <v>322.94</v>
       </c>
-      <c r="K80" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
       <c r="A81" s="2">
         <v>42115</v>
       </c>
@@ -3249,11 +3372,13 @@
       <c r="J81">
         <v>1603</v>
       </c>
-      <c r="K81" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
       <c r="A82" s="2">
         <v>42116</v>
       </c>
@@ -3284,11 +3409,13 @@
       <c r="J82">
         <v>728</v>
       </c>
-      <c r="K82" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
       <c r="A83" s="2">
         <v>42117</v>
       </c>
@@ -3319,11 +3446,13 @@
       <c r="J83">
         <v>2008.88</v>
       </c>
-      <c r="K83" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
       <c r="A84" s="2">
         <v>42118</v>
       </c>
@@ -3354,11 +3483,13 @@
       <c r="J84">
         <v>1230</v>
       </c>
-      <c r="K84" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
       <c r="A85" s="2">
         <v>42121</v>
       </c>
@@ -3389,11 +3520,13 @@
       <c r="J85">
         <v>860</v>
       </c>
-      <c r="K85" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
       <c r="A86" s="2">
         <v>42122</v>
       </c>
@@ -3424,11 +3557,13 @@
       <c r="J86">
         <v>15935</v>
       </c>
-      <c r="K86" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
       <c r="A87" s="2">
         <v>42123</v>
       </c>
@@ -3459,11 +3594,13 @@
       <c r="J87">
         <v>1865</v>
       </c>
-      <c r="K87" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
       <c r="A88" s="2">
         <v>42124</v>
       </c>
@@ -3494,16 +3631,18 @@
       <c r="J88">
         <v>121.22</v>
       </c>
-      <c r="K88" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
       <c r="A89" s="2">
         <v>42128</v>
       </c>
       <c r="B89">
-        <v>1304.1600000000001</v>
+        <v>1304.16</v>
       </c>
       <c r="C89">
         <v>60</v>
@@ -3529,11 +3668,13 @@
       <c r="J89">
         <v>1364.16</v>
       </c>
-      <c r="K89" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
       <c r="A90" s="2">
         <v>42129</v>
       </c>
@@ -3564,11 +3705,13 @@
       <c r="J90">
         <v>9.66</v>
       </c>
-      <c r="K90" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
       <c r="A91" s="2">
         <v>42130</v>
       </c>
@@ -3599,11 +3742,13 @@
       <c r="J91">
         <v>420</v>
       </c>
-      <c r="K91" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
       <c r="A92" s="2">
         <v>42131</v>
       </c>
@@ -3634,11 +3779,13 @@
       <c r="J92">
         <v>30</v>
       </c>
-      <c r="K92" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
       <c r="A93" s="2">
         <v>42132</v>
       </c>
@@ -3669,11 +3816,13 @@
       <c r="J93">
         <v>10521.84</v>
       </c>
-      <c r="K93" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
       <c r="A94" s="2">
         <v>42135</v>
       </c>
@@ -3704,11 +3853,13 @@
       <c r="J94">
         <v>240.78</v>
       </c>
-      <c r="K94" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
       <c r="A95" s="2">
         <v>42136</v>
       </c>
@@ -3739,11 +3890,13 @@
       <c r="J95">
         <v>80</v>
       </c>
-      <c r="K95" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
       <c r="A96" s="2">
         <v>42137</v>
       </c>
@@ -3774,11 +3927,13 @@
       <c r="J96">
         <v>175</v>
       </c>
-      <c r="K96" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
       <c r="A97" s="2">
         <v>42138</v>
       </c>
@@ -3809,11 +3964,13 @@
       <c r="J97">
         <v>8827</v>
       </c>
-      <c r="K97" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
       <c r="A98" s="2">
         <v>42139</v>
       </c>
@@ -3844,11 +4001,13 @@
       <c r="J98">
         <v>180</v>
       </c>
-      <c r="K98" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
       <c r="A99" s="2">
         <v>42142</v>
       </c>
@@ -3879,11 +4038,13 @@
       <c r="J99">
         <v>517</v>
       </c>
-      <c r="K99" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
       <c r="A100" s="2">
         <v>42143</v>
       </c>
@@ -3914,11 +4075,13 @@
       <c r="J100">
         <v>2210</v>
       </c>
-      <c r="K100" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
       <c r="A101" s="2">
         <v>42144</v>
       </c>
@@ -3949,11 +4112,13 @@
       <c r="J101">
         <v>30</v>
       </c>
-      <c r="K101" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
       <c r="A102" s="2">
         <v>42150</v>
       </c>
@@ -3984,11 +4149,13 @@
       <c r="J102">
         <v>180</v>
       </c>
-      <c r="K102" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
       <c r="A103" s="2">
         <v>42151</v>
       </c>
@@ -4019,11 +4186,13 @@
       <c r="J103">
         <v>417.38</v>
       </c>
-      <c r="K103" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
       <c r="A104" s="2">
         <v>42153</v>
       </c>
@@ -4054,11 +4223,13 @@
       <c r="J104">
         <v>108</v>
       </c>
-      <c r="K104" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
       <c r="A105" s="2">
         <v>42156</v>
       </c>
@@ -4089,11 +4260,13 @@
       <c r="J105">
         <v>11.37</v>
       </c>
-      <c r="K105" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
       <c r="A106" s="2">
         <v>42157</v>
       </c>
@@ -4124,11 +4297,13 @@
       <c r="J106">
         <v>7760</v>
       </c>
-      <c r="K106" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
       <c r="A107" s="2">
         <v>42158</v>
       </c>
@@ -4159,16 +4334,18 @@
       <c r="J107">
         <v>120</v>
       </c>
-      <c r="K107" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
       <c r="A108" s="2">
         <v>42159</v>
       </c>
       <c r="B108">
-        <v>1229.8399999999999</v>
+        <v>1229.84</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -4177,7 +4354,7 @@
         <v>0</v>
       </c>
       <c r="E108">
-        <v>1229.8399999999999</v>
+        <v>1229.84</v>
       </c>
       <c r="F108">
         <v>0</v>
@@ -4192,13 +4369,15 @@
         <v>0</v>
       </c>
       <c r="J108">
-        <v>1229.8399999999999</v>
-      </c>
-      <c r="K108" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
+        <v>1229.84</v>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
       <c r="A109" s="2">
         <v>42160</v>
       </c>
@@ -4229,11 +4408,13 @@
       <c r="J109">
         <v>1690</v>
       </c>
-      <c r="K109" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
       <c r="A110" s="2">
         <v>42161</v>
       </c>
@@ -4264,11 +4445,13 @@
       <c r="J110">
         <v>69.75</v>
       </c>
-      <c r="K110" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
       <c r="A111" s="2">
         <v>42163</v>
       </c>
@@ -4299,11 +4482,13 @@
       <c r="J111">
         <v>9685.9</v>
       </c>
-      <c r="K111" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
       <c r="A112" s="2">
         <v>42164</v>
       </c>
@@ -4334,11 +4519,13 @@
       <c r="J112">
         <v>470</v>
       </c>
-      <c r="K112" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
       <c r="A113" s="2">
         <v>42165</v>
       </c>
@@ -4369,11 +4556,13 @@
       <c r="J113">
         <v>377.02</v>
       </c>
-      <c r="K113" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
       <c r="A114" s="2">
         <v>42166</v>
       </c>
@@ -4404,11 +4593,13 @@
       <c r="J114">
         <v>210</v>
       </c>
-      <c r="K114" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
       <c r="A115" s="2">
         <v>42167</v>
       </c>
@@ -4439,11 +4630,13 @@
       <c r="J115">
         <v>988</v>
       </c>
-      <c r="K115" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
       <c r="A116" s="2">
         <v>42170</v>
       </c>
@@ -4474,11 +4667,13 @@
       <c r="J116">
         <v>1319.4</v>
       </c>
-      <c r="K116" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
       <c r="A117" s="2">
         <v>42171</v>
       </c>
@@ -4509,11 +4704,13 @@
       <c r="J117">
         <v>802.45</v>
       </c>
-      <c r="K117" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
       <c r="A118" s="2">
         <v>42172</v>
       </c>
@@ -4544,11 +4741,13 @@
       <c r="J118">
         <v>43023</v>
       </c>
-      <c r="K118" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
       <c r="A119" s="2">
         <v>42173</v>
       </c>
@@ -4579,11 +4778,13 @@
       <c r="J119">
         <v>338.86</v>
       </c>
-      <c r="K119" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
       <c r="A120" s="2">
         <v>42174</v>
       </c>
@@ -4614,11 +4815,13 @@
       <c r="J120">
         <v>600</v>
       </c>
-      <c r="K120" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
       <c r="A121" s="2">
         <v>42177</v>
       </c>
@@ -4649,11 +4852,13 @@
       <c r="J121">
         <v>488</v>
       </c>
-      <c r="K121" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
       <c r="A122" s="2">
         <v>42178</v>
       </c>
@@ -4684,11 +4889,13 @@
       <c r="J122">
         <v>707.79</v>
       </c>
-      <c r="K122" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
       <c r="A123" s="2">
         <v>42179</v>
       </c>
@@ -4719,11 +4926,13 @@
       <c r="J123">
         <v>210</v>
       </c>
-      <c r="K123" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
       <c r="A124" s="2">
         <v>42180</v>
       </c>
@@ -4737,7 +4946,7 @@
         <v>0</v>
       </c>
       <c r="E124">
-        <v>666.31999999999994</v>
+        <v>666.3199999999999</v>
       </c>
       <c r="F124">
         <v>0</v>
@@ -4752,13 +4961,15 @@
         <v>-216</v>
       </c>
       <c r="J124">
-        <v>450.31999999999988</v>
-      </c>
-      <c r="K124" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
+        <v>450.3199999999999</v>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
       <c r="A125" s="2">
         <v>42181</v>
       </c>
@@ -4789,11 +5000,13 @@
       <c r="J125">
         <v>148.65</v>
       </c>
-      <c r="K125" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
       <c r="A126" s="2">
         <v>42184</v>
       </c>
@@ -4824,11 +5037,13 @@
       <c r="J126">
         <v>810</v>
       </c>
-      <c r="K126" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
       <c r="A127" s="2">
         <v>42185</v>
       </c>
@@ -4859,11 +5074,13 @@
       <c r="J127">
         <v>2817.79</v>
       </c>
-      <c r="K127" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
       <c r="A128" s="2">
         <v>42186</v>
       </c>
@@ -4894,11 +5111,13 @@
       <c r="J128">
         <v>570</v>
       </c>
-      <c r="K128" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
       <c r="A129" s="2">
         <v>42187</v>
       </c>
@@ -4929,11 +5148,13 @@
       <c r="J129">
         <v>270</v>
       </c>
-      <c r="K129" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
       <c r="A130" s="2">
         <v>42188</v>
       </c>
@@ -4964,11 +5185,13 @@
       <c r="J130">
         <v>540</v>
       </c>
-      <c r="K130" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
       <c r="A131" s="2">
         <v>42191</v>
       </c>
@@ -4999,11 +5222,13 @@
       <c r="J131">
         <v>166.83</v>
       </c>
-      <c r="K131" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
       <c r="A132" s="2">
         <v>42192</v>
       </c>
@@ -5034,11 +5259,13 @@
       <c r="J132">
         <v>824.36</v>
       </c>
-      <c r="K132" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
       <c r="A133" s="2">
         <v>42193</v>
       </c>
@@ -5069,11 +5296,13 @@
       <c r="J133">
         <v>390</v>
       </c>
-      <c r="K133" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
       <c r="A134" s="2">
         <v>42195</v>
       </c>
@@ -5104,11 +5333,13 @@
       <c r="J134">
         <v>5780</v>
       </c>
-      <c r="K134" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
       <c r="A135" s="2">
         <v>42199</v>
       </c>
@@ -5139,11 +5370,13 @@
       <c r="J135">
         <v>255</v>
       </c>
-      <c r="K135" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
       <c r="A136" s="2">
         <v>42200</v>
       </c>
@@ -5174,11 +5407,13 @@
       <c r="J136">
         <v>560</v>
       </c>
-      <c r="K136" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
       <c r="A137" s="2">
         <v>42202</v>
       </c>
@@ -5209,11 +5444,13 @@
       <c r="J137">
         <v>0</v>
       </c>
-      <c r="K137" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
       <c r="A138" s="2">
         <v>42205</v>
       </c>
@@ -5244,11 +5481,13 @@
       <c r="J138">
         <v>859</v>
       </c>
-      <c r="K138" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
       <c r="A139" s="2">
         <v>42206</v>
       </c>
@@ -5279,11 +5518,13 @@
       <c r="J139">
         <v>60.12</v>
       </c>
-      <c r="K139" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
       <c r="A140" s="2">
         <v>42207</v>
       </c>
@@ -5314,11 +5555,13 @@
       <c r="J140">
         <v>7000</v>
       </c>
-      <c r="K140" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
       <c r="A141" s="2">
         <v>42208</v>
       </c>
@@ -5349,16 +5592,18 @@
       <c r="J141">
         <v>30</v>
       </c>
-      <c r="K141" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
       <c r="A142" s="2">
         <v>42209</v>
       </c>
       <c r="B142">
-        <v>69.900000000000006</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="C142">
         <v>0</v>
@@ -5367,7 +5612,7 @@
         <v>0</v>
       </c>
       <c r="E142">
-        <v>69.900000000000006</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="F142">
         <v>0</v>
@@ -5382,13 +5627,15 @@
         <v>0</v>
       </c>
       <c r="J142">
-        <v>69.900000000000006</v>
-      </c>
-      <c r="K142" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
       <c r="A143" s="2">
         <v>42213</v>
       </c>
@@ -5419,11 +5666,13 @@
       <c r="J143">
         <v>270</v>
       </c>
-      <c r="K143" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
       <c r="A144" s="2">
         <v>42214</v>
       </c>
@@ -5454,11 +5703,13 @@
       <c r="J144">
         <v>30</v>
       </c>
-      <c r="K144" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
       <c r="A145" s="2">
         <v>42215</v>
       </c>
@@ -5489,11 +5740,13 @@
       <c r="J145">
         <v>2700.06</v>
       </c>
-      <c r="K145" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
       <c r="A146" s="2">
         <v>42216</v>
       </c>
@@ -5524,11 +5777,13 @@
       <c r="J146">
         <v>663.85</v>
       </c>
-      <c r="K146" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
       <c r="A147" s="2">
         <v>42219</v>
       </c>
@@ -5559,11 +5814,13 @@
       <c r="J147">
         <v>197.44</v>
       </c>
-      <c r="K147" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
       <c r="A148" s="2">
         <v>42220</v>
       </c>
@@ -5594,11 +5851,13 @@
       <c r="J148">
         <v>50</v>
       </c>
-      <c r="K148" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
       <c r="A149" s="2">
         <v>42221</v>
       </c>
@@ -5629,11 +5888,13 @@
       <c r="J149">
         <v>1148</v>
       </c>
-      <c r="K149" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
       <c r="A150" s="2">
         <v>42222</v>
       </c>
@@ -5664,11 +5925,13 @@
       <c r="J150">
         <v>880</v>
       </c>
-      <c r="K150" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
       <c r="A151" s="2">
         <v>42223</v>
       </c>
@@ -5699,11 +5962,13 @@
       <c r="J151">
         <v>1985</v>
       </c>
-      <c r="K151" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
       <c r="A152" s="2">
         <v>42226</v>
       </c>
@@ -5734,11 +5999,13 @@
       <c r="J152">
         <v>270</v>
       </c>
-      <c r="K152" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
       <c r="A153" s="2">
         <v>42227</v>
       </c>
@@ -5769,11 +6036,13 @@
       <c r="J153">
         <v>180</v>
       </c>
-      <c r="K153" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
       <c r="A154" s="2">
         <v>42228</v>
       </c>
@@ -5804,11 +6073,13 @@
       <c r="J154">
         <v>210</v>
       </c>
-      <c r="K154" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
       <c r="A155" s="2">
         <v>42229</v>
       </c>
@@ -5839,11 +6110,13 @@
       <c r="J155">
         <v>181.12</v>
       </c>
-      <c r="K155" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
       <c r="A156" s="2">
         <v>42230</v>
       </c>
@@ -5872,13 +6145,15 @@
         <v>11.46</v>
       </c>
       <c r="J156">
-        <v>702.16000000000008</v>
-      </c>
-      <c r="K156" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
+        <v>702.1600000000001</v>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
       <c r="A157" s="2">
         <v>42234</v>
       </c>
@@ -5909,11 +6184,13 @@
       <c r="J157">
         <v>2028</v>
       </c>
-      <c r="K157" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
       <c r="A158" s="2">
         <v>42235</v>
       </c>
@@ -5944,11 +6221,13 @@
       <c r="J158">
         <v>540</v>
       </c>
-      <c r="K158" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
       <c r="A159" s="2">
         <v>42236</v>
       </c>
@@ -5979,11 +6258,13 @@
       <c r="J159">
         <v>300.94</v>
       </c>
-      <c r="K159" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
       <c r="A160" s="2">
         <v>42237</v>
       </c>
@@ -6014,11 +6295,13 @@
       <c r="J160">
         <v>5841.15</v>
       </c>
-      <c r="K160" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
       <c r="A161" s="2">
         <v>42247</v>
       </c>
@@ -6049,11 +6332,13 @@
       <c r="J161">
         <v>707.75</v>
       </c>
-      <c r="K161" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
       <c r="A162" s="2">
         <v>42248</v>
       </c>
@@ -6084,11 +6369,13 @@
       <c r="J162">
         <v>118.14</v>
       </c>
-      <c r="K162" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
       <c r="A163" s="2">
         <v>42250</v>
       </c>
@@ -6119,11 +6406,13 @@
       <c r="J163">
         <v>210</v>
       </c>
-      <c r="K163" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
       <c r="A164" s="2">
         <v>42251</v>
       </c>
@@ -6154,11 +6443,13 @@
       <c r="J164">
         <v>950</v>
       </c>
-      <c r="K164" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
       <c r="A165" s="2">
         <v>42254</v>
       </c>
@@ -6189,11 +6480,13 @@
       <c r="J165">
         <v>-205.34</v>
       </c>
-      <c r="K165" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
       <c r="A166" s="2">
         <v>42255</v>
       </c>
@@ -6224,11 +6517,13 @@
       <c r="J166">
         <v>210</v>
       </c>
-      <c r="K166" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
       <c r="A167" s="2">
         <v>42256</v>
       </c>
@@ -6259,11 +6554,13 @@
       <c r="J167">
         <v>30</v>
       </c>
-      <c r="K167" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
       <c r="A168" s="2">
         <v>42257</v>
       </c>
@@ -6294,11 +6591,13 @@
       <c r="J168">
         <v>84.66</v>
       </c>
-      <c r="K168" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
       <c r="A169" s="2">
         <v>42261</v>
       </c>
@@ -6329,11 +6628,13 @@
       <c r="J169">
         <v>154.43</v>
       </c>
-      <c r="K169" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
       <c r="A170" s="2">
         <v>42262</v>
       </c>
@@ -6364,11 +6665,13 @@
       <c r="J170">
         <v>150</v>
       </c>
-      <c r="K170" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
       <c r="A171" s="2">
         <v>42263</v>
       </c>
@@ -6399,11 +6702,13 @@
       <c r="J171">
         <v>270</v>
       </c>
-      <c r="K171" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
       <c r="A172" s="2">
         <v>42264</v>
       </c>
@@ -6434,11 +6739,13 @@
       <c r="J172">
         <v>213</v>
       </c>
-      <c r="K172" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
       <c r="A173" s="2">
         <v>42265</v>
       </c>
@@ -6469,11 +6776,13 @@
       <c r="J173">
         <v>90</v>
       </c>
-      <c r="K173" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
       <c r="A174" s="2">
         <v>42268</v>
       </c>
@@ -6504,11 +6813,13 @@
       <c r="J174">
         <v>65.81</v>
       </c>
-      <c r="K174" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
       <c r="A175" s="2">
         <v>42269</v>
       </c>
@@ -6539,11 +6850,13 @@
       <c r="J175">
         <v>150</v>
       </c>
-      <c r="K175" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
       <c r="A176" s="2">
         <v>42270</v>
       </c>
@@ -6574,11 +6887,13 @@
       <c r="J176">
         <v>68.7</v>
       </c>
-      <c r="K176" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
       <c r="A177" s="2">
         <v>42271</v>
       </c>
@@ -6609,11 +6924,13 @@
       <c r="J177">
         <v>800</v>
       </c>
-      <c r="K177" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
       <c r="A178" s="2">
         <v>42272</v>
       </c>
@@ -6644,16 +6961,18 @@
       <c r="J178">
         <v>34.22</v>
       </c>
-      <c r="K178" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
       <c r="A179" s="2">
         <v>42275</v>
       </c>
       <c r="B179">
-        <v>938.68</v>
+        <v>938.6799999999999</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -6662,7 +6981,7 @@
         <v>0</v>
       </c>
       <c r="E179">
-        <v>938.68</v>
+        <v>938.6799999999999</v>
       </c>
       <c r="F179">
         <v>0</v>
@@ -6677,13 +6996,15 @@
         <v>0</v>
       </c>
       <c r="J179">
-        <v>938.68</v>
-      </c>
-      <c r="K179" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
+        <v>938.6799999999999</v>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
       <c r="A180" s="2">
         <v>42276</v>
       </c>
@@ -6714,11 +7035,13 @@
       <c r="J180">
         <v>316.74</v>
       </c>
-      <c r="K180" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
       <c r="A181" s="2">
         <v>42277</v>
       </c>
@@ -6749,16 +7072,18 @@
       <c r="J181">
         <v>450</v>
       </c>
-      <c r="K181" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
       <c r="A182" s="2">
         <v>42278</v>
       </c>
       <c r="B182">
-        <v>2.2400000000000002</v>
+        <v>2.24</v>
       </c>
       <c r="C182">
         <v>0</v>
@@ -6767,7 +7092,7 @@
         <v>0</v>
       </c>
       <c r="E182">
-        <v>2.2400000000000002</v>
+        <v>2.24</v>
       </c>
       <c r="F182">
         <v>0</v>
@@ -6782,13 +7107,15 @@
         <v>0</v>
       </c>
       <c r="J182">
-        <v>2.2400000000000002</v>
-      </c>
-      <c r="K182" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
+        <v>2.24</v>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
       <c r="A183" s="2">
         <v>42279</v>
       </c>
@@ -6819,11 +7146,13 @@
       <c r="J183">
         <v>270</v>
       </c>
-      <c r="K183" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
       <c r="A184" s="2">
         <v>42282</v>
       </c>
@@ -6854,11 +7183,13 @@
       <c r="J184">
         <v>1274.74</v>
       </c>
-      <c r="K184" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
       <c r="A185" s="2">
         <v>42283</v>
       </c>
@@ -6889,11 +7220,13 @@
       <c r="J185">
         <v>524.71</v>
       </c>
-      <c r="K185" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
       <c r="A186" s="2">
         <v>42284</v>
       </c>
@@ -6924,11 +7257,13 @@
       <c r="J186">
         <v>736.62</v>
       </c>
-      <c r="K186" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
       <c r="A187" s="2">
         <v>42285</v>
       </c>
@@ -6959,11 +7294,13 @@
       <c r="J187">
         <v>2144.54</v>
       </c>
-      <c r="K187" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
       <c r="A188" s="2">
         <v>42286</v>
       </c>
@@ -6994,16 +7331,18 @@
       <c r="J188">
         <v>328.25</v>
       </c>
-      <c r="K188" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
       <c r="A189" s="2">
         <v>42291</v>
       </c>
       <c r="B189">
-        <v>147.19999999999999</v>
+        <v>147.2</v>
       </c>
       <c r="C189">
         <v>0</v>
@@ -7012,7 +7351,7 @@
         <v>0</v>
       </c>
       <c r="E189">
-        <v>147.19999999999999</v>
+        <v>147.2</v>
       </c>
       <c r="F189">
         <v>0</v>
@@ -7027,13 +7366,15 @@
         <v>0</v>
       </c>
       <c r="J189">
-        <v>147.19999999999999</v>
-      </c>
-      <c r="K189" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
+        <v>147.2</v>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
       <c r="A190" s="2">
         <v>42292</v>
       </c>
@@ -7064,11 +7405,13 @@
       <c r="J190">
         <v>150</v>
       </c>
-      <c r="K190" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
       <c r="A191" s="2">
         <v>42293</v>
       </c>
@@ -7099,11 +7442,13 @@
       <c r="J191">
         <v>206.3</v>
       </c>
-      <c r="K191" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
       <c r="A192" s="2">
         <v>42296</v>
       </c>
@@ -7134,11 +7479,13 @@
       <c r="J192">
         <v>370</v>
       </c>
-      <c r="K192" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
       <c r="A193" s="2">
         <v>42297</v>
       </c>
@@ -7169,11 +7516,13 @@
       <c r="J193">
         <v>207.42</v>
       </c>
-      <c r="K193" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
       <c r="A194" s="2">
         <v>42298</v>
       </c>
@@ -7204,11 +7553,13 @@
       <c r="J194">
         <v>616</v>
       </c>
-      <c r="K194" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
       <c r="A195" s="2">
         <v>42299</v>
       </c>
@@ -7239,16 +7590,18 @@
       <c r="J195">
         <v>800</v>
       </c>
-      <c r="K195" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
       <c r="A196" s="2">
         <v>42300</v>
       </c>
       <c r="B196">
-        <v>266.16000000000003</v>
+        <v>266.16</v>
       </c>
       <c r="C196">
         <v>0</v>
@@ -7274,11 +7627,13 @@
       <c r="J196">
         <v>116.16</v>
       </c>
-      <c r="K196" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
       <c r="A197" s="2">
         <v>42303</v>
       </c>
@@ -7309,11 +7664,13 @@
       <c r="J197">
         <v>230.94</v>
       </c>
-      <c r="K197" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
       <c r="A198" s="2">
         <v>42304</v>
       </c>
@@ -7344,11 +7701,13 @@
       <c r="J198">
         <v>1163.08</v>
       </c>
-      <c r="K198" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
       <c r="A199" s="2">
         <v>42305</v>
       </c>
@@ -7379,11 +7738,13 @@
       <c r="J199">
         <v>10</v>
       </c>
-      <c r="K199" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
       <c r="A200" s="2">
         <v>42306</v>
       </c>
@@ -7414,11 +7775,13 @@
       <c r="J200">
         <v>694.24</v>
       </c>
-      <c r="K200" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
       <c r="A201" s="2">
         <v>42307</v>
       </c>
@@ -7449,11 +7812,13 @@
       <c r="J201">
         <v>194.42</v>
       </c>
-      <c r="K201" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
       <c r="A202" s="2">
         <v>42310</v>
       </c>
@@ -7484,11 +7849,13 @@
       <c r="J202">
         <v>510</v>
       </c>
-      <c r="K202" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
       <c r="A203" s="2">
         <v>42311</v>
       </c>
@@ -7519,11 +7886,13 @@
       <c r="J203">
         <v>517.14</v>
       </c>
-      <c r="K203" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
       <c r="A204" s="2">
         <v>42312</v>
       </c>
@@ -7554,11 +7923,13 @@
       <c r="J204">
         <v>180</v>
       </c>
-      <c r="K204" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
       <c r="A205" s="2">
         <v>42313</v>
       </c>
@@ -7589,11 +7960,13 @@
       <c r="J205">
         <v>2180.59</v>
       </c>
-      <c r="K205" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
       <c r="A206" s="2">
         <v>42314</v>
       </c>
@@ -7624,11 +7997,13 @@
       <c r="J206">
         <v>874</v>
       </c>
-      <c r="K206" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
       <c r="A207" s="2">
         <v>42317</v>
       </c>
@@ -7659,11 +8034,13 @@
       <c r="J207">
         <v>369</v>
       </c>
-      <c r="K207" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
       <c r="A208" s="2">
         <v>42318</v>
       </c>
@@ -7694,11 +8071,13 @@
       <c r="J208">
         <v>1388</v>
       </c>
-      <c r="K208" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
       <c r="A209" s="2">
         <v>42319</v>
       </c>
@@ -7729,11 +8108,13 @@
       <c r="J209">
         <v>1367.72</v>
       </c>
-      <c r="K209" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
       <c r="A210" s="2">
         <v>42320</v>
       </c>
@@ -7764,11 +8145,13 @@
       <c r="J210">
         <v>1754.86</v>
       </c>
-      <c r="K210" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
       <c r="A211" s="2">
         <v>42321</v>
       </c>
@@ -7799,11 +8182,13 @@
       <c r="J211">
         <v>1100</v>
       </c>
-      <c r="K211" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
       <c r="A212" s="2">
         <v>42324</v>
       </c>
@@ -7817,7 +8202,7 @@
         <v>0</v>
       </c>
       <c r="E212">
-        <v>518.91999999999996</v>
+        <v>518.92</v>
       </c>
       <c r="F212">
         <v>0</v>
@@ -7832,13 +8217,15 @@
         <v>0</v>
       </c>
       <c r="J212">
-        <v>518.91999999999996</v>
-      </c>
-      <c r="K212" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.3">
+        <v>518.92</v>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
       <c r="A213" s="2">
         <v>42325</v>
       </c>
@@ -7869,11 +8256,13 @@
       <c r="J213">
         <v>2015.25</v>
       </c>
-      <c r="K213" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
       <c r="A214" s="2">
         <v>42326</v>
       </c>
@@ -7904,11 +8293,13 @@
       <c r="J214">
         <v>358.78</v>
       </c>
-      <c r="K214" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="215" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
       <c r="A215" s="2">
         <v>42327</v>
       </c>
@@ -7939,11 +8330,13 @@
       <c r="J215">
         <v>35.5</v>
       </c>
-      <c r="K215" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="216" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
       <c r="A216" s="2">
         <v>42328</v>
       </c>
@@ -7974,11 +8367,13 @@
       <c r="J216">
         <v>1440</v>
       </c>
-      <c r="K216" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="217" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
       <c r="A217" s="2">
         <v>42331</v>
       </c>
@@ -8009,11 +8404,13 @@
       <c r="J217">
         <v>60</v>
       </c>
-      <c r="K217" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="218" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
       <c r="A218" s="2">
         <v>42332</v>
       </c>
@@ -8044,11 +8441,13 @@
       <c r="J218">
         <v>2337.84</v>
       </c>
-      <c r="K218" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
       <c r="A219" s="2">
         <v>42333</v>
       </c>
@@ -8079,16 +8478,18 @@
       <c r="J219">
         <v>1507.32</v>
       </c>
-      <c r="K219" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
       <c r="A220" s="2">
         <v>42334</v>
       </c>
       <c r="B220">
-        <v>645.04999999999995</v>
+        <v>645.05</v>
       </c>
       <c r="C220">
         <v>27.52</v>
@@ -8097,7 +8498,7 @@
         <v>0</v>
       </c>
       <c r="E220">
-        <v>672.56999999999994</v>
+        <v>672.5699999999999</v>
       </c>
       <c r="F220">
         <v>0</v>
@@ -8112,13 +8513,15 @@
         <v>0</v>
       </c>
       <c r="J220">
-        <v>672.56999999999994</v>
-      </c>
-      <c r="K220" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.3">
+        <v>672.5699999999999</v>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
       <c r="A221" s="2">
         <v>42338</v>
       </c>
@@ -8149,16 +8552,18 @@
       <c r="J221">
         <v>656.5</v>
       </c>
-      <c r="K221" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
       <c r="A222" s="2">
         <v>42339</v>
       </c>
       <c r="B222">
-        <v>1179.1400000000001</v>
+        <v>1179.14</v>
       </c>
       <c r="C222">
         <v>0</v>
@@ -8167,7 +8572,7 @@
         <v>0</v>
       </c>
       <c r="E222">
-        <v>1179.1400000000001</v>
+        <v>1179.14</v>
       </c>
       <c r="F222">
         <v>0</v>
@@ -8182,13 +8587,15 @@
         <v>0</v>
       </c>
       <c r="J222">
-        <v>1179.1400000000001</v>
-      </c>
-      <c r="K222" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.3">
+        <v>1179.14</v>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
       <c r="A223" s="2">
         <v>42340</v>
       </c>
@@ -8219,11 +8626,13 @@
       <c r="J223">
         <v>2530</v>
       </c>
-      <c r="K223" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
       <c r="A224" s="2">
         <v>42341</v>
       </c>
@@ -8254,11 +8663,13 @@
       <c r="J224">
         <v>799.92</v>
       </c>
-      <c r="K224" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="225" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
       <c r="A225" s="2">
         <v>42342</v>
       </c>
@@ -8289,16 +8700,18 @@
       <c r="J225">
         <v>2066.92</v>
       </c>
-      <c r="K225" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
       <c r="A226" s="2">
         <v>42343</v>
       </c>
       <c r="B226">
-        <v>67.949999999999989</v>
+        <v>67.94999999999999</v>
       </c>
       <c r="C226">
         <v>0</v>
@@ -8307,7 +8720,7 @@
         <v>0</v>
       </c>
       <c r="E226">
-        <v>67.949999999999989</v>
+        <v>67.94999999999999</v>
       </c>
       <c r="F226">
         <v>0</v>
@@ -8322,13 +8735,15 @@
         <v>0</v>
       </c>
       <c r="J226">
-        <v>67.949999999999989</v>
-      </c>
-      <c r="K226" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.3">
+        <v>67.94999999999999</v>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
       <c r="A227" s="2">
         <v>42347</v>
       </c>
@@ -8359,11 +8774,13 @@
       <c r="J227">
         <v>5105.16</v>
       </c>
-      <c r="K227" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="228" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
       <c r="A228" s="2">
         <v>42348</v>
       </c>
@@ -8394,11 +8811,13 @@
       <c r="J228">
         <v>12273.98</v>
       </c>
-      <c r="K228" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
       <c r="A229" s="2">
         <v>42349</v>
       </c>
@@ -8429,11 +8848,13 @@
       <c r="J229">
         <v>17450</v>
       </c>
-      <c r="K229" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
       <c r="A230" s="2">
         <v>42352</v>
       </c>
@@ -8464,11 +8885,13 @@
       <c r="J230">
         <v>28752.38</v>
       </c>
-      <c r="K230" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
       <c r="A231" s="2">
         <v>42353</v>
       </c>
@@ -8499,11 +8922,13 @@
       <c r="J231">
         <v>17061.82</v>
       </c>
-      <c r="K231" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
       <c r="A232" s="2">
         <v>42354</v>
       </c>
@@ -8534,11 +8959,13 @@
       <c r="J232">
         <v>48444.55</v>
       </c>
-      <c r="K232" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="233" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
       <c r="A233" s="2">
         <v>42355</v>
       </c>
@@ -8552,7 +8979,7 @@
         <v>200</v>
       </c>
       <c r="E233">
-        <v>35838.080000000002</v>
+        <v>35838.08</v>
       </c>
       <c r="F233">
         <v>1150</v>
@@ -8567,13 +8994,15 @@
         <v>1150</v>
       </c>
       <c r="J233">
-        <v>36988.080000000002</v>
-      </c>
-      <c r="K233" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="234" spans="1:11" x14ac:dyDescent="0.3">
+        <v>36988.08</v>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
       <c r="A234" s="2">
         <v>42356</v>
       </c>
@@ -8604,11 +9033,13 @@
       <c r="J234">
         <v>54442.82</v>
       </c>
-      <c r="K234" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
       <c r="A235" s="2">
         <v>42357</v>
       </c>
@@ -8639,11 +9070,13 @@
       <c r="J235">
         <v>240</v>
       </c>
-      <c r="K235" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
       <c r="A236" s="2">
         <v>42359</v>
       </c>
@@ -8674,11 +9107,13 @@
       <c r="J236">
         <v>54030.47</v>
       </c>
-      <c r="K236" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
       <c r="A237" s="2">
         <v>42360</v>
       </c>
@@ -8709,16 +9144,18 @@
       <c r="J237">
         <v>52522.71</v>
       </c>
-      <c r="K237" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
       <c r="A238" s="2">
         <v>42361</v>
       </c>
       <c r="B238">
-        <v>20936.830000000002</v>
+        <v>20936.83</v>
       </c>
       <c r="C238">
         <v>720</v>
@@ -8744,11 +9181,13 @@
       <c r="J238">
         <v>22056.83</v>
       </c>
-      <c r="K238" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
       <c r="A239" s="2">
         <v>42362</v>
       </c>
@@ -8779,11 +9218,13 @@
       <c r="J239">
         <v>5810</v>
       </c>
-      <c r="K239" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
       <c r="A240" s="2">
         <v>42364</v>
       </c>
@@ -8814,11 +9255,13 @@
       <c r="J240">
         <v>330</v>
       </c>
-      <c r="K240" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
       <c r="A241" s="2">
         <v>42366</v>
       </c>
@@ -8849,11 +9292,13 @@
       <c r="J241">
         <v>58684.87</v>
       </c>
-      <c r="K241" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="242" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
       <c r="A242" s="2">
         <v>42367</v>
       </c>
@@ -8884,11 +9329,13 @@
       <c r="J242">
         <v>60001.16</v>
       </c>
-      <c r="K242" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="243" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
       <c r="A243" s="2">
         <v>42368</v>
       </c>
@@ -8919,11 +9366,13 @@
       <c r="J243">
         <v>43635.19</v>
       </c>
-      <c r="K243" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="244" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
       <c r="A244" s="2">
         <v>42369</v>
       </c>
@@ -8954,8 +9403,10 @@
       <c r="J244">
         <v>300</v>
       </c>
-      <c r="K244" t="s">
-        <v>11</v>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
       </c>
     </row>
   </sheetData>
